--- a/Excel/StockQuotation (7).xlsx
+++ b/Excel/StockQuotation (7).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>03/02/23 12:59:01</v>
+        <v>07/02/23 23:30:28</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>162.55</v>
+        <v>161.33</v>
       </c>
       <c r="B7" t="str">
-        <v>-0.33 (-0.2026%)</v>
+        <v>-0.24 (-0.1485%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>162.88</v>
+        <v>161.89</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>162.14</v>
+        <v>160.8</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>4330988</v>
+        <v>11943384</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>47731557.7</v>
+        <v>141280206.7</v>
       </c>
     </row>
     <row r="9">
@@ -534,22 +534,22 @@
         <v>-</v>
       </c>
       <c r="C11">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="D11">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.9433962264150944</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="G11">
-        <v>5.35</v>
+        <v>5.55</v>
       </c>
       <c r="H11">
-        <v>5.25</v>
+        <v>5.45</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -558,22 +558,22 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>20300</v>
+        <v>379547</v>
       </c>
       <c r="L11">
-        <v>108.057</v>
+        <v>2082.2345</v>
       </c>
       <c r="M11">
-        <v>20500</v>
+        <v>66000</v>
       </c>
       <c r="N11">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O11">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="P11">
-        <v>7300</v>
+        <v>49700</v>
       </c>
     </row>
     <row r="12">
@@ -584,13 +584,13 @@
         <v>-</v>
       </c>
       <c r="C12">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>-0.8064516129032258</v>
       </c>
       <c r="F12">
         <v>12.4</v>
@@ -599,31 +599,31 @@
         <v>12.4</v>
       </c>
       <c r="H12">
+        <v>12.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>122600</v>
+      </c>
+      <c r="L12">
+        <v>1508.11</v>
+      </c>
+      <c r="M12">
+        <v>239200</v>
+      </c>
+      <c r="N12">
+        <v>12.3</v>
+      </c>
+      <c r="O12">
         <v>12.4</v>
       </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>7200</v>
-      </c>
-      <c r="L12">
-        <v>89.28</v>
-      </c>
-      <c r="M12">
-        <v>3900</v>
-      </c>
-      <c r="N12">
-        <v>12.4</v>
-      </c>
-      <c r="O12">
-        <v>12.5</v>
-      </c>
       <c r="P12">
-        <v>107300</v>
+        <v>81500</v>
       </c>
     </row>
     <row r="13">
@@ -634,46 +634,46 @@
         <v>-</v>
       </c>
       <c r="C13">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="D13">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>0.6711409395973155</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>7.45</v>
       </c>
       <c r="G13">
-        <v>7.55</v>
+        <v>7.45</v>
       </c>
       <c r="H13">
+        <v>7.35</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>187400</v>
+      </c>
+      <c r="L13">
+        <v>1386.47</v>
+      </c>
+      <c r="M13">
+        <v>121800</v>
+      </c>
+      <c r="N13">
+        <v>7.35</v>
+      </c>
+      <c r="O13">
         <v>7.4</v>
       </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>170600</v>
-      </c>
-      <c r="L13">
-        <v>1275.715</v>
-      </c>
-      <c r="M13">
-        <v>135900</v>
-      </c>
-      <c r="N13">
-        <v>7.45</v>
-      </c>
-      <c r="O13">
-        <v>7.5</v>
-      </c>
       <c r="P13">
-        <v>50000</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="14">
@@ -684,7 +684,7 @@
         <v>-</v>
       </c>
       <c r="C14">
-        <v>6.8</v>
+        <v>6.85</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>6.8</v>
+        <v>6.85</v>
       </c>
       <c r="G14">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H14">
         <v>6.8</v>
@@ -708,22 +708,22 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>92320</v>
+        <v>283475</v>
       </c>
       <c r="L14">
-        <v>627.776</v>
+        <v>1940.41375</v>
       </c>
       <c r="M14">
-        <v>18200</v>
+        <v>39800</v>
       </c>
       <c r="N14">
-        <v>6.8</v>
+        <v>6.85</v>
       </c>
       <c r="O14">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="P14">
-        <v>36300</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="15">
@@ -737,16 +737,16 @@
         <v>9.95</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>0.5050505050505051</v>
       </c>
       <c r="F15">
-        <v>9.95</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>9.95</v>
+        <v>10</v>
       </c>
       <c r="H15">
         <v>9.95</v>
@@ -758,13 +758,13 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>18700</v>
+        <v>31601</v>
       </c>
       <c r="L15">
-        <v>186.065</v>
+        <v>314.457</v>
       </c>
       <c r="M15">
-        <v>107900</v>
+        <v>110000</v>
       </c>
       <c r="N15">
         <v>9.9</v>
@@ -773,7 +773,7 @@
         <v>9.95</v>
       </c>
       <c r="P15">
-        <v>11300</v>
+        <v>365900</v>
       </c>
     </row>
     <row r="16">
@@ -784,7 +784,7 @@
         <v>-</v>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -793,7 +793,7 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="G16">
         <v>11</v>
@@ -808,13 +808,13 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>24254</v>
+        <v>1366768</v>
       </c>
       <c r="L16">
-        <v>265.234</v>
+        <v>14899.828</v>
       </c>
       <c r="M16">
-        <v>977100</v>
+        <v>878500</v>
       </c>
       <c r="N16">
         <v>10.9</v>
@@ -823,7 +823,7 @@
         <v>11</v>
       </c>
       <c r="P16">
-        <v>1101900</v>
+        <v>1906500</v>
       </c>
     </row>
     <row r="17">
@@ -834,22 +834,22 @@
         <v>-</v>
       </c>
       <c r="C17">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="D17">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>-1.9047619047619047</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="G17">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="H17">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -858,13 +858,13 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="L17">
-        <v>2.06</v>
+        <v>2.1215</v>
       </c>
       <c r="M17">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="N17">
         <v>10.4</v>
@@ -873,7 +873,7 @@
         <v>10.5</v>
       </c>
       <c r="P17">
-        <v>6100</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="18">
@@ -884,23 +884,23 @@
         <v>-</v>
       </c>
       <c r="C18">
-        <v>8.3</v>
+        <v>8.4</v>
       </c>
       <c r="D18">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>0.6060606060606061</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>8.2</v>
+        <v>8.45</v>
       </c>
       <c r="G18">
+        <v>8.45</v>
+      </c>
+      <c r="H18">
         <v>8.35</v>
       </c>
-      <c r="H18">
-        <v>8.2</v>
-      </c>
       <c r="I18">
         <v>0</v>
       </c>
@@ -908,22 +908,22 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>205800</v>
+        <v>12902</v>
       </c>
       <c r="L18">
-        <v>1704.63</v>
+        <v>108.1569</v>
       </c>
       <c r="M18">
-        <v>46900</v>
+        <v>2900</v>
       </c>
       <c r="N18">
-        <v>8.3</v>
+        <v>8.4</v>
       </c>
       <c r="O18">
-        <v>8.35</v>
+        <v>8.45</v>
       </c>
       <c r="P18">
-        <v>99800</v>
+        <v>14600</v>
       </c>
     </row>
     <row r="19">
@@ -949,7 +949,7 @@
         <v>11.7</v>
       </c>
       <c r="H19">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -958,13 +958,13 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>44210</v>
+        <v>165600</v>
       </c>
       <c r="L19">
-        <v>517.257</v>
+        <v>1935.49</v>
       </c>
       <c r="M19">
-        <v>238500</v>
+        <v>226900</v>
       </c>
       <c r="N19">
         <v>11.6</v>
@@ -973,7 +973,7 @@
         <v>11.7</v>
       </c>
       <c r="P19">
-        <v>375800</v>
+        <v>291600</v>
       </c>
     </row>
     <row r="20">
@@ -984,22 +984,22 @@
         <v>-</v>
       </c>
       <c r="C20">
-        <v>19.3</v>
+        <v>18.5</v>
       </c>
       <c r="D20">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E20">
-        <v>-0.5154639175257731</v>
+        <v>-1.0695187165775402</v>
       </c>
       <c r="F20">
-        <v>19.4</v>
+        <v>18.7</v>
       </c>
       <c r="G20">
-        <v>19.4</v>
+        <v>18.7</v>
       </c>
       <c r="H20">
-        <v>19.1</v>
+        <v>18.3</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1008,22 +1008,22 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>749383</v>
+        <v>2548603</v>
       </c>
       <c r="L20">
-        <v>14418.2366</v>
+        <v>46882.963200000006</v>
       </c>
       <c r="M20">
-        <v>400</v>
+        <v>35600</v>
       </c>
       <c r="N20">
-        <v>19.2</v>
+        <v>18.4</v>
       </c>
       <c r="O20">
-        <v>19.3</v>
+        <v>18.5</v>
       </c>
       <c r="P20">
-        <v>94900</v>
+        <v>379300</v>
       </c>
     </row>
     <row r="21">
@@ -1034,22 +1034,22 @@
         <v>-</v>
       </c>
       <c r="C21">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="F21">
-        <v>7.4</v>
+        <v>7.55</v>
       </c>
       <c r="G21">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="H21">
-        <v>7.4</v>
+        <v>7.55</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1058,22 +1058,22 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>101500</v>
+        <v>693623</v>
       </c>
       <c r="L21">
-        <v>751.1</v>
+        <v>5312.93745</v>
       </c>
       <c r="M21">
-        <v>98600</v>
+        <v>800</v>
       </c>
       <c r="N21">
-        <v>7.4</v>
+        <v>7.65</v>
       </c>
       <c r="O21">
-        <v>7.45</v>
+        <v>7.7</v>
       </c>
       <c r="P21">
-        <v>36900</v>
+        <v>103600</v>
       </c>
     </row>
     <row r="22">
@@ -1087,10 +1087,10 @@
         <v>5.35</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>0.9433962264150944</v>
       </c>
       <c r="F22">
         <v>5.35</v>
@@ -1108,13 +1108,13 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>20000</v>
+        <v>100</v>
       </c>
       <c r="L22">
-        <v>107</v>
+        <v>0.535</v>
       </c>
       <c r="M22">
-        <v>15900</v>
+        <v>14300</v>
       </c>
       <c r="N22">
         <v>5.3</v>
@@ -1123,7 +1123,7 @@
         <v>5.35</v>
       </c>
       <c r="P22">
-        <v>38500</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="23">
@@ -1134,46 +1134,46 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="D23">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E23">
-        <v>0.8</v>
+        <v>-0.8</v>
       </c>
       <c r="F23">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="G23">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="H23">
+        <v>6.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>31005</v>
+      </c>
+      <c r="L23">
+        <v>192.38629999999998</v>
+      </c>
+      <c r="M23">
+        <v>7000</v>
+      </c>
+      <c r="N23">
+        <v>6.2</v>
+      </c>
+      <c r="O23">
         <v>6.25</v>
       </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>10700</v>
-      </c>
-      <c r="L23">
-        <v>66.905</v>
-      </c>
-      <c r="M23">
-        <v>23900</v>
-      </c>
-      <c r="N23">
-        <v>6.25</v>
-      </c>
-      <c r="O23">
-        <v>6.3</v>
-      </c>
       <c r="P23">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24">
@@ -1184,19 +1184,19 @@
         <v>-</v>
       </c>
       <c r="C24">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="D24">
         <v>0.04</v>
       </c>
       <c r="E24">
-        <v>0.9345794392523364</v>
+        <v>0.9302325581395349</v>
       </c>
       <c r="F24">
         <v>4.28</v>
       </c>
       <c r="G24">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="H24">
         <v>4.28</v>
@@ -1208,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>160400</v>
+        <v>398900</v>
       </c>
       <c r="L24">
-        <v>690.39</v>
+        <v>1713.952</v>
       </c>
       <c r="M24">
-        <v>76100</v>
+        <v>162400</v>
       </c>
       <c r="N24">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="O24">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="P24">
-        <v>5700</v>
+        <v>17300</v>
       </c>
     </row>
     <row r="25">
@@ -1237,16 +1237,16 @@
         <v>11.7</v>
       </c>
       <c r="D25">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E25">
-        <v>-0.847457627118644</v>
+        <v>-1.680672268907563</v>
       </c>
       <c r="F25">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="G25">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="H25">
         <v>11.7</v>
@@ -1258,13 +1258,13 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>70600</v>
+        <v>196402</v>
       </c>
       <c r="L25">
-        <v>828.43</v>
+        <v>2314.854</v>
       </c>
       <c r="M25">
-        <v>144600</v>
+        <v>79900</v>
       </c>
       <c r="N25">
         <v>11.7</v>
@@ -1273,7 +1273,7 @@
         <v>11.8</v>
       </c>
       <c r="P25">
-        <v>250900</v>
+        <v>167800</v>
       </c>
     </row>
     <row r="26">
@@ -1283,47 +1283,47 @@
       <c r="B26" t="str">
         <v>-</v>
       </c>
-      <c r="C26" t="str">
-        <v>-</v>
-      </c>
-      <c r="D26" t="str">
-        <v>-</v>
-      </c>
-      <c r="E26" t="str">
-        <v>-</v>
-      </c>
-      <c r="F26" t="str">
-        <v>-</v>
-      </c>
-      <c r="G26" t="str">
-        <v>-</v>
-      </c>
-      <c r="H26" t="str">
-        <v>-</v>
-      </c>
-      <c r="I26" t="str">
-        <v>-</v>
-      </c>
-      <c r="J26" t="str">
-        <v>-</v>
-      </c>
-      <c r="K26" t="str">
-        <v>-</v>
-      </c>
-      <c r="L26" t="str">
-        <v>-</v>
+      <c r="C26">
+        <v>15</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>15</v>
+      </c>
+      <c r="G26">
+        <v>15</v>
+      </c>
+      <c r="H26">
+        <v>14.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>195600</v>
+      </c>
+      <c r="L26">
+        <v>2930.42</v>
       </c>
       <c r="M26">
-        <v>132700</v>
+        <v>47700</v>
       </c>
       <c r="N26">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="O26">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="P26">
-        <v>20500</v>
+        <v>48600</v>
       </c>
     </row>
     <row r="27">
@@ -1337,10 +1337,10 @@
         <v>8.6</v>
       </c>
       <c r="D27">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E27">
-        <v>-0.5780346820809249</v>
+        <v>0.5847953216374269</v>
       </c>
       <c r="F27">
         <v>8.6</v>
@@ -1358,22 +1358,22 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>3701</v>
+        <v>5000</v>
       </c>
       <c r="L27">
-        <v>31.828599999999998</v>
+        <v>43</v>
       </c>
       <c r="M27">
-        <v>2800</v>
+        <v>5700</v>
       </c>
       <c r="N27">
-        <v>8.55</v>
+        <v>8.5</v>
       </c>
       <c r="O27">
         <v>8.6</v>
       </c>
       <c r="P27">
-        <v>1300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1384,13 +1384,13 @@
         <v>-</v>
       </c>
       <c r="C28">
-        <v>9.85</v>
+        <v>9.8</v>
       </c>
       <c r="D28">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>0.5102040816326531</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>9.8</v>
@@ -1408,13 +1408,13 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>30400</v>
+        <v>122400</v>
       </c>
       <c r="L28">
-        <v>298.92</v>
+        <v>1202.06</v>
       </c>
       <c r="M28">
-        <v>12300</v>
+        <v>1200</v>
       </c>
       <c r="N28">
         <v>9.8</v>
@@ -1423,7 +1423,7 @@
         <v>9.85</v>
       </c>
       <c r="P28">
-        <v>32600</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="29">
@@ -1434,46 +1434,46 @@
         <v>-</v>
       </c>
       <c r="C29">
+        <v>9.8</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>9.8</v>
+      </c>
+      <c r="G29">
+        <v>9.85</v>
+      </c>
+      <c r="H29">
+        <v>9.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>417700</v>
+      </c>
+      <c r="L29">
+        <v>4095.57</v>
+      </c>
+      <c r="M29">
+        <v>23800</v>
+      </c>
+      <c r="N29">
         <v>9.75</v>
       </c>
-      <c r="D29">
-        <v>0.05</v>
-      </c>
-      <c r="E29">
-        <v>0.5154639175257731</v>
-      </c>
-      <c r="F29">
-        <v>9.65</v>
-      </c>
-      <c r="G29">
+      <c r="O29">
         <v>9.8</v>
       </c>
-      <c r="H29">
-        <v>9.6</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>337061</v>
-      </c>
-      <c r="L29">
-        <v>3263.79975</v>
-      </c>
-      <c r="M29">
-        <v>152400</v>
-      </c>
-      <c r="N29">
-        <v>9.7</v>
-      </c>
-      <c r="O29">
-        <v>9.75</v>
-      </c>
       <c r="P29">
-        <v>16400</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="30">
@@ -1484,7 +1484,7 @@
         <v>-</v>
       </c>
       <c r="C30">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1499,7 +1499,7 @@
         <v>4.8</v>
       </c>
       <c r="H30">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1508,13 +1508,13 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>7000</v>
+        <v>8800</v>
       </c>
       <c r="L30">
-        <v>33.6</v>
+        <v>42.084</v>
       </c>
       <c r="M30">
-        <v>3000</v>
+        <v>17200</v>
       </c>
       <c r="N30">
         <v>4.78</v>
@@ -1523,7 +1523,7 @@
         <v>4.8</v>
       </c>
       <c r="P30">
-        <v>7500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="31">
@@ -1546,7 +1546,7 @@
         <v>10.2</v>
       </c>
       <c r="G31">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="H31">
         <v>10.2</v>
@@ -1558,13 +1558,13 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>5300</v>
+        <v>40300</v>
       </c>
       <c r="L31">
-        <v>54.06</v>
+        <v>411.07</v>
       </c>
       <c r="M31">
-        <v>135400</v>
+        <v>104300</v>
       </c>
       <c r="N31">
         <v>10.2</v>
@@ -1573,7 +1573,7 @@
         <v>10.3</v>
       </c>
       <c r="P31">
-        <v>90900</v>
+        <v>95900</v>
       </c>
     </row>
     <row r="32">
@@ -1584,22 +1584,22 @@
         <v>-</v>
       </c>
       <c r="C32">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="D32">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>-0.7092198581560284</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>14.1</v>
+        <v>13.7</v>
       </c>
       <c r="G32">
-        <v>14.1</v>
+        <v>13.8</v>
       </c>
       <c r="H32">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1608,22 +1608,22 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>17500</v>
+        <v>911982</v>
       </c>
       <c r="L32">
-        <v>246.45</v>
+        <v>12508.3183</v>
       </c>
       <c r="M32">
-        <v>194100</v>
+        <v>65900</v>
       </c>
       <c r="N32">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="O32">
-        <v>14.1</v>
+        <v>13.8</v>
       </c>
       <c r="P32">
-        <v>146100</v>
+        <v>265300</v>
       </c>
     </row>
     <row r="33">
@@ -1634,46 +1634,46 @@
         <v>-</v>
       </c>
       <c r="C33">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="D33">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="E33">
-        <v>-0.8620689655172413</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="F33">
+        <v>11.7</v>
+      </c>
+      <c r="G33">
+        <v>11.7</v>
+      </c>
+      <c r="H33">
         <v>11.6</v>
       </c>
-      <c r="G33">
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>88906</v>
+      </c>
+      <c r="L33">
+        <v>1035.4102</v>
+      </c>
+      <c r="M33">
+        <v>36900</v>
+      </c>
+      <c r="N33">
         <v>11.6</v>
       </c>
-      <c r="H33">
-        <v>11.5</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>120400</v>
-      </c>
-      <c r="L33">
-        <v>1387.88</v>
-      </c>
-      <c r="M33">
-        <v>51000</v>
-      </c>
-      <c r="N33">
-        <v>11.5</v>
-      </c>
       <c r="O33">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="P33">
-        <v>10500</v>
+        <v>61600</v>
       </c>
     </row>
     <row r="34">
@@ -1714,16 +1714,16 @@
         <v>-</v>
       </c>
       <c r="M34">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="N34">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="O34">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="P34">
-        <v>200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="35">
@@ -1737,19 +1737,19 @@
         <v>8.85</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="F35">
-        <v>8.85</v>
+        <v>8.75</v>
       </c>
       <c r="G35">
         <v>8.85</v>
       </c>
       <c r="H35">
-        <v>8.85</v>
+        <v>8.75</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1758,22 +1758,22 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>33100</v>
+        <v>69300</v>
       </c>
       <c r="L35">
-        <v>292.935</v>
+        <v>606.66</v>
       </c>
       <c r="M35">
-        <v>800</v>
+        <v>8000</v>
       </c>
       <c r="N35">
-        <v>8.8</v>
+        <v>8.75</v>
       </c>
       <c r="O35">
         <v>8.85</v>
       </c>
       <c r="P35">
-        <v>600</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="36">
@@ -1784,46 +1784,46 @@
         <v>-</v>
       </c>
       <c r="C36">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="D36">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E36">
-        <v>1.4814814814814814</v>
+        <v>-0.7299270072992701</v>
       </c>
       <c r="F36">
+        <v>13.8</v>
+      </c>
+      <c r="G36">
+        <v>13.8</v>
+      </c>
+      <c r="H36">
+        <v>13.6</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>352500</v>
+      </c>
+      <c r="L36">
+        <v>4830.33</v>
+      </c>
+      <c r="M36">
+        <v>131000</v>
+      </c>
+      <c r="N36">
         <v>13.5</v>
       </c>
-      <c r="G36">
-        <v>13.7</v>
-      </c>
-      <c r="H36">
-        <v>13.5</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>54400</v>
-      </c>
-      <c r="L36">
-        <v>742.15</v>
-      </c>
-      <c r="M36">
-        <v>25100</v>
-      </c>
-      <c r="N36">
+      <c r="O36">
         <v>13.6</v>
       </c>
-      <c r="O36">
-        <v>13.7</v>
-      </c>
       <c r="P36">
-        <v>102600</v>
+        <v>334600</v>
       </c>
     </row>
     <row r="37">
@@ -1837,10 +1837,10 @@
         <v>6.6</v>
       </c>
       <c r="D37">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>-0.7518796992481203</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>6.6</v>
@@ -1858,22 +1858,22 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>100</v>
+        <v>18300</v>
       </c>
       <c r="L37">
-        <v>0.66</v>
+        <v>120.78</v>
       </c>
       <c r="M37">
-        <v>7900</v>
+        <v>5600</v>
       </c>
       <c r="N37">
+        <v>6.55</v>
+      </c>
+      <c r="O37">
         <v>6.6</v>
       </c>
-      <c r="O37">
-        <v>6.65</v>
-      </c>
       <c r="P37">
-        <v>45200</v>
+        <v>700</v>
       </c>
     </row>
     <row r="38">
@@ -1884,7 +1884,7 @@
         <v>-</v>
       </c>
       <c r="C38">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -1893,13 +1893,13 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="G38">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="H38">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -1908,22 +1908,22 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>2448</v>
+        <v>3252</v>
       </c>
       <c r="L38">
-        <v>30.110400000000002</v>
+        <v>39.349199999999996</v>
       </c>
       <c r="M38">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="N38">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="O38">
         <v>12.3</v>
       </c>
       <c r="P38">
-        <v>4000</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="39">
@@ -1937,19 +1937,19 @@
         <v>14.2</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1.4285714285714286</v>
       </c>
       <c r="F39">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="G39">
         <v>14.3</v>
       </c>
       <c r="H39">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -1958,13 +1958,13 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>93600</v>
+        <v>366099</v>
       </c>
       <c r="L39">
-        <v>1336.27</v>
+        <v>5189.57</v>
       </c>
       <c r="M39">
-        <v>78600</v>
+        <v>1400</v>
       </c>
       <c r="N39">
         <v>14.2</v>
@@ -1973,7 +1973,7 @@
         <v>14.3</v>
       </c>
       <c r="P39">
-        <v>2100</v>
+        <v>356800</v>
       </c>
     </row>
     <row r="40">
@@ -1987,43 +1987,43 @@
         <v>7.55</v>
       </c>
       <c r="D40">
-        <v>-0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="E40">
-        <v>-1.948051948051948</v>
+        <v>-0.6578947368421053</v>
       </c>
       <c r="F40">
-        <v>7.55</v>
+        <v>7.45</v>
       </c>
       <c r="G40">
         <v>7.55</v>
       </c>
       <c r="H40">
+        <v>7.45</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>46700</v>
+      </c>
+      <c r="L40">
+        <v>350.72</v>
+      </c>
+      <c r="M40">
+        <v>5000</v>
+      </c>
+      <c r="N40">
+        <v>7.5</v>
+      </c>
+      <c r="O40">
         <v>7.55</v>
       </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>200</v>
-      </c>
-      <c r="L40">
-        <v>1.51</v>
-      </c>
-      <c r="M40">
-        <v>500</v>
-      </c>
-      <c r="N40">
-        <v>7.6</v>
-      </c>
-      <c r="O40">
-        <v>7.65</v>
-      </c>
       <c r="P40">
-        <v>800</v>
+        <v>8800</v>
       </c>
     </row>
     <row r="41">
@@ -2033,47 +2033,47 @@
       <c r="B41" t="str">
         <v>-</v>
       </c>
-      <c r="C41" t="str">
-        <v>-</v>
-      </c>
-      <c r="D41" t="str">
-        <v>-</v>
-      </c>
-      <c r="E41" t="str">
-        <v>-</v>
-      </c>
-      <c r="F41" t="str">
-        <v>-</v>
-      </c>
-      <c r="G41" t="str">
-        <v>-</v>
-      </c>
-      <c r="H41" t="str">
-        <v>-</v>
-      </c>
-      <c r="I41" t="str">
-        <v>-</v>
-      </c>
-      <c r="J41" t="str">
-        <v>-</v>
-      </c>
-      <c r="K41" t="str">
-        <v>-</v>
-      </c>
-      <c r="L41" t="str">
-        <v>-</v>
+      <c r="C41">
+        <v>7.4</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>7.4</v>
+      </c>
+      <c r="G41">
+        <v>7.4</v>
+      </c>
+      <c r="H41">
+        <v>7.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>1015</v>
+      </c>
+      <c r="L41">
+        <v>7.5095</v>
       </c>
       <c r="M41">
-        <v>200</v>
+        <v>5800</v>
       </c>
       <c r="N41">
-        <v>7.35</v>
+        <v>7.4</v>
       </c>
       <c r="O41">
         <v>7.45</v>
       </c>
       <c r="P41">
-        <v>10100</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="42">
@@ -2084,22 +2084,22 @@
         <v>-</v>
       </c>
       <c r="C42">
-        <v>4.36</v>
+        <v>4.76</v>
       </c>
       <c r="D42">
-        <v>0.24</v>
+        <v>-0.1</v>
       </c>
       <c r="E42">
-        <v>5.825242718446602</v>
+        <v>-2.05761316872428</v>
       </c>
       <c r="F42">
-        <v>4.3</v>
+        <v>4.46</v>
       </c>
       <c r="G42">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="H42">
-        <v>4.3</v>
+        <v>4.46</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2108,22 +2108,22 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>1500</v>
+        <v>6200</v>
       </c>
       <c r="L42">
-        <v>6.544</v>
+        <v>29.216</v>
       </c>
       <c r="M42">
-        <v>10400</v>
+        <v>4000</v>
       </c>
       <c r="N42">
-        <v>4.36</v>
+        <v>4.5</v>
       </c>
       <c r="O42">
-        <v>4.4</v>
+        <v>4.78</v>
       </c>
       <c r="P42">
-        <v>1400</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="43">
@@ -2134,22 +2134,22 @@
         <v>-</v>
       </c>
       <c r="C43">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>-0.819672131147541</v>
       </c>
       <c r="F43">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="G43">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="H43">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2158,22 +2158,22 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>20000</v>
+        <v>3600</v>
       </c>
       <c r="L43">
-        <v>122</v>
+        <v>21.88</v>
       </c>
       <c r="M43">
-        <v>1100</v>
+        <v>2500</v>
       </c>
       <c r="N43">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="O43">
         <v>6.15</v>
       </c>
       <c r="P43">
-        <v>8800</v>
+        <v>14100</v>
       </c>
     </row>
     <row r="44">
@@ -2217,7 +2217,7 @@
         <v>100</v>
       </c>
       <c r="N44">
-        <v>13</v>
+        <v>12.3</v>
       </c>
       <c r="O44">
         <v>18.7</v>
@@ -2234,46 +2234,46 @@
         <v>-</v>
       </c>
       <c r="C45">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>-0.5747126436781609</v>
       </c>
       <c r="F45">
         <v>1.74</v>
       </c>
       <c r="G45">
+        <v>1.75</v>
+      </c>
+      <c r="H45">
+        <v>1.71</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>42700</v>
+      </c>
+      <c r="L45">
+        <v>73.722</v>
+      </c>
+      <c r="M45">
+        <v>15500</v>
+      </c>
+      <c r="N45">
+        <v>1.71</v>
+      </c>
+      <c r="O45">
         <v>1.74</v>
       </c>
-      <c r="H45">
-        <v>1.74</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>6200</v>
-      </c>
-      <c r="L45">
-        <v>10.788</v>
-      </c>
-      <c r="M45">
-        <v>3700</v>
-      </c>
-      <c r="N45">
-        <v>1.73</v>
-      </c>
-      <c r="O45">
-        <v>1.75</v>
-      </c>
       <c r="P45">
-        <v>16400</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="46">
@@ -2284,22 +2284,22 @@
         <v>-</v>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="D46">
         <v>0.05</v>
       </c>
       <c r="E46">
-        <v>0.8403361344537815</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F46">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="G46">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="H46">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2308,22 +2308,22 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>11700</v>
+        <v>32711</v>
       </c>
       <c r="L46">
-        <v>70.2</v>
+        <v>196.171</v>
       </c>
       <c r="M46">
-        <v>4000</v>
+        <v>19000</v>
       </c>
       <c r="N46">
         <v>5.95</v>
       </c>
       <c r="O46">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="P46">
-        <v>3000</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="47">
@@ -2367,13 +2367,13 @@
         <v>500</v>
       </c>
       <c r="N47">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="O47">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="P47">
-        <v>10000</v>
+        <v>15200</v>
       </c>
     </row>
     <row r="48">
@@ -2414,7 +2414,7 @@
         <v>-</v>
       </c>
       <c r="M48">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="N48">
         <v>4.92</v>
@@ -2423,7 +2423,7 @@
         <v>4.98</v>
       </c>
       <c r="P48">
-        <v>11500</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="49">
@@ -2433,38 +2433,38 @@
       <c r="B49" t="str">
         <v>-</v>
       </c>
-      <c r="C49" t="str">
-        <v>-</v>
-      </c>
-      <c r="D49" t="str">
-        <v>-</v>
-      </c>
-      <c r="E49" t="str">
-        <v>-</v>
-      </c>
-      <c r="F49" t="str">
-        <v>-</v>
-      </c>
-      <c r="G49" t="str">
-        <v>-</v>
-      </c>
-      <c r="H49" t="str">
-        <v>-</v>
-      </c>
-      <c r="I49" t="str">
-        <v>-</v>
-      </c>
-      <c r="J49" t="str">
-        <v>-</v>
-      </c>
-      <c r="K49" t="str">
-        <v>-</v>
-      </c>
-      <c r="L49" t="str">
-        <v>-</v>
+      <c r="C49">
+        <v>2.84</v>
+      </c>
+      <c r="D49">
+        <v>0.02</v>
+      </c>
+      <c r="E49">
+        <v>0.7092198581560284</v>
+      </c>
+      <c r="F49">
+        <v>2.84</v>
+      </c>
+      <c r="G49">
+        <v>2.84</v>
+      </c>
+      <c r="H49">
+        <v>2.84</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>100</v>
+      </c>
+      <c r="L49">
+        <v>0.284</v>
       </c>
       <c r="M49">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="N49">
         <v>2.82</v>
@@ -2508,13 +2508,13 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>205600</v>
+        <v>435600</v>
       </c>
       <c r="L50">
-        <v>2388.2</v>
+        <v>5095.62</v>
       </c>
       <c r="M50">
-        <v>143300</v>
+        <v>204600</v>
       </c>
       <c r="N50">
         <v>11.6</v>
@@ -2523,7 +2523,7 @@
         <v>11.7</v>
       </c>
       <c r="P50">
-        <v>385900</v>
+        <v>399400</v>
       </c>
     </row>
     <row r="51">
@@ -2549,7 +2549,7 @@
         <v>11.5</v>
       </c>
       <c r="H51">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2558,13 +2558,13 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>53600</v>
+        <v>63300</v>
       </c>
       <c r="L51">
-        <v>608.4</v>
+        <v>721.95</v>
       </c>
       <c r="M51">
-        <v>41400</v>
+        <v>25100</v>
       </c>
       <c r="N51">
         <v>11.4</v>
@@ -2573,7 +2573,7 @@
         <v>11.5</v>
       </c>
       <c r="P51">
-        <v>3800</v>
+        <v>46700</v>
       </c>
     </row>
     <row r="52">
@@ -2587,43 +2587,43 @@
         <v>9.6</v>
       </c>
       <c r="D52">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="E52">
-        <v>-0.5181347150259067</v>
+        <v>-1.0309278350515463</v>
       </c>
       <c r="F52">
-        <v>9.65</v>
+        <v>9.6</v>
       </c>
       <c r="G52">
         <v>9.65</v>
       </c>
       <c r="H52">
+        <v>9.55</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>585855</v>
+      </c>
+      <c r="L52">
+        <v>5619.803</v>
+      </c>
+      <c r="M52">
+        <v>2200</v>
+      </c>
+      <c r="N52">
+        <v>9.55</v>
+      </c>
+      <c r="O52">
         <v>9.6</v>
       </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <v>73600</v>
-      </c>
-      <c r="L52">
-        <v>706.59</v>
-      </c>
-      <c r="M52">
-        <v>3800</v>
-      </c>
-      <c r="N52">
-        <v>9.65</v>
-      </c>
-      <c r="O52">
-        <v>9.7</v>
-      </c>
       <c r="P52">
-        <v>30500</v>
+        <v>67500</v>
       </c>
     </row>
     <row r="53">
@@ -2634,19 +2634,19 @@
         <v>-</v>
       </c>
       <c r="C53">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="D53">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>0.7633587786259542</v>
+        <v>0</v>
       </c>
       <c r="F53">
         <v>6.5</v>
       </c>
       <c r="G53">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="H53">
         <v>6.5</v>
@@ -2658,22 +2658,22 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>6200</v>
+        <v>16000</v>
       </c>
       <c r="L53">
-        <v>40.56</v>
+        <v>104.05</v>
       </c>
       <c r="M53">
-        <v>30700</v>
+        <v>42400</v>
       </c>
       <c r="N53">
         <v>6.5</v>
       </c>
       <c r="O53">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="P53">
-        <v>15700</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="54">
@@ -2683,47 +2683,47 @@
       <c r="B54" t="str">
         <v>-</v>
       </c>
-      <c r="C54" t="str">
-        <v>-</v>
-      </c>
-      <c r="D54" t="str">
-        <v>-</v>
-      </c>
-      <c r="E54" t="str">
-        <v>-</v>
-      </c>
-      <c r="F54" t="str">
-        <v>-</v>
-      </c>
-      <c r="G54" t="str">
-        <v>-</v>
-      </c>
-      <c r="H54" t="str">
-        <v>-</v>
-      </c>
-      <c r="I54" t="str">
-        <v>-</v>
-      </c>
-      <c r="J54" t="str">
-        <v>-</v>
-      </c>
-      <c r="K54" t="str">
-        <v>-</v>
-      </c>
-      <c r="L54" t="str">
-        <v>-</v>
+      <c r="C54">
+        <v>2.94</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>2.88</v>
+      </c>
+      <c r="G54">
+        <v>2.94</v>
+      </c>
+      <c r="H54">
+        <v>2.82</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>2500</v>
+      </c>
+      <c r="L54">
+        <v>7.122</v>
       </c>
       <c r="M54">
-        <v>60200</v>
+        <v>2000</v>
       </c>
       <c r="N54">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="O54">
         <v>2.94</v>
       </c>
       <c r="P54">
-        <v>2000</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="55">
@@ -2737,43 +2737,43 @@
         <v>9.35</v>
       </c>
       <c r="D55">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E55">
-        <v>-0.5319148936170213</v>
+        <v>0</v>
       </c>
       <c r="F55">
         <v>9.35</v>
       </c>
       <c r="G55">
-        <v>9.4</v>
+        <v>9.35</v>
       </c>
       <c r="H55">
+        <v>9.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>202348</v>
+      </c>
+      <c r="L55">
+        <v>1889.32965</v>
+      </c>
+      <c r="M55">
+        <v>209100</v>
+      </c>
+      <c r="N55">
+        <v>9.3</v>
+      </c>
+      <c r="O55">
         <v>9.35</v>
       </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>239380</v>
-      </c>
-      <c r="L55">
-        <v>2246.717</v>
-      </c>
-      <c r="M55">
-        <v>106900</v>
-      </c>
-      <c r="N55">
-        <v>9.35</v>
-      </c>
-      <c r="O55">
-        <v>9.4</v>
-      </c>
       <c r="P55">
-        <v>175800</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="56">
@@ -2784,22 +2784,22 @@
         <v>NP</v>
       </c>
       <c r="C56">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="D56">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>0.6024096385542169</v>
+        <v>0</v>
       </c>
       <c r="F56">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="G56">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="H56">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2808,22 +2808,22 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>200</v>
+        <v>11600</v>
       </c>
       <c r="L56">
-        <v>0.668</v>
+        <v>39.44</v>
       </c>
       <c r="M56">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="N56">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="O56">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="P56">
-        <v>1000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="57">
@@ -2833,23 +2833,23 @@
       <c r="B57" t="str">
         <v>-</v>
       </c>
-      <c r="C57" t="str">
-        <v>-</v>
-      </c>
-      <c r="D57" t="str">
-        <v>-</v>
-      </c>
-      <c r="E57" t="str">
-        <v>-</v>
-      </c>
-      <c r="F57" t="str">
-        <v>-</v>
-      </c>
-      <c r="G57" t="str">
-        <v>-</v>
-      </c>
-      <c r="H57" t="str">
-        <v>-</v>
+      <c r="C57">
+        <v>8</v>
+      </c>
+      <c r="D57">
+        <v>-0.15</v>
+      </c>
+      <c r="E57">
+        <v>-1.8404907975460123</v>
+      </c>
+      <c r="F57">
+        <v>8</v>
+      </c>
+      <c r="G57">
+        <v>8</v>
+      </c>
+      <c r="H57">
+        <v>8</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2858,22 +2858,22 @@
         <v>0</v>
       </c>
       <c r="K57">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="L57">
-        <v>0.0805</v>
+        <v>2.4</v>
       </c>
       <c r="M57">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="N57">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O57">
-        <v>8.05</v>
+        <v>8.4</v>
       </c>
       <c r="P57">
-        <v>200</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="58">
@@ -2884,22 +2884,22 @@
         <v>-</v>
       </c>
       <c r="C58">
-        <v>7.25</v>
+        <v>7.3</v>
       </c>
       <c r="D58">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>0.6944444444444444</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="G58">
-        <v>7.25</v>
+        <v>7.35</v>
       </c>
       <c r="H58">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2908,22 +2908,22 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>135600</v>
+        <v>47215</v>
       </c>
       <c r="L58">
-        <v>979.745</v>
+        <v>347.01525</v>
       </c>
       <c r="M58">
-        <v>63500</v>
+        <v>70800</v>
       </c>
       <c r="N58">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="O58">
-        <v>7.25</v>
+        <v>7.35</v>
       </c>
       <c r="P58">
-        <v>11500</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="59">
@@ -2937,19 +2937,19 @@
         <v>7.3</v>
       </c>
       <c r="D59">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>-0.6802721088435374</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>7.35</v>
+        <v>7.25</v>
       </c>
       <c r="G59">
         <v>7.35</v>
       </c>
       <c r="H59">
-        <v>7.3</v>
+        <v>7.25</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2958,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>41305</v>
+        <v>16500</v>
       </c>
       <c r="L59">
-        <v>302.542</v>
+        <v>120.405</v>
       </c>
       <c r="M59">
-        <v>7800</v>
+        <v>5800</v>
       </c>
       <c r="N59">
         <v>7.25</v>
@@ -2973,7 +2973,7 @@
         <v>7.3</v>
       </c>
       <c r="P59">
-        <v>12300</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="60">
@@ -2983,47 +2983,47 @@
       <c r="B60" t="str">
         <v>-</v>
       </c>
-      <c r="C60">
-        <v>7.15</v>
-      </c>
-      <c r="D60">
-        <v>0.15</v>
-      </c>
-      <c r="E60">
-        <v>2.142857142857143</v>
-      </c>
-      <c r="F60">
-        <v>7.15</v>
-      </c>
-      <c r="G60">
-        <v>7.15</v>
-      </c>
-      <c r="H60">
-        <v>7.15</v>
-      </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60">
-        <v>0</v>
-      </c>
-      <c r="K60">
+      <c r="C60" t="str">
+        <v>-</v>
+      </c>
+      <c r="D60" t="str">
+        <v>-</v>
+      </c>
+      <c r="E60" t="str">
+        <v>-</v>
+      </c>
+      <c r="F60" t="str">
+        <v>-</v>
+      </c>
+      <c r="G60" t="str">
+        <v>-</v>
+      </c>
+      <c r="H60" t="str">
+        <v>-</v>
+      </c>
+      <c r="I60" t="str">
+        <v>-</v>
+      </c>
+      <c r="J60" t="str">
+        <v>-</v>
+      </c>
+      <c r="K60" t="str">
+        <v>-</v>
+      </c>
+      <c r="L60" t="str">
+        <v>-</v>
+      </c>
+      <c r="M60">
+        <v>1000</v>
+      </c>
+      <c r="N60">
+        <v>7.05</v>
+      </c>
+      <c r="O60">
+        <v>7.1</v>
+      </c>
+      <c r="P60">
         <v>100</v>
-      </c>
-      <c r="L60">
-        <v>0.715</v>
-      </c>
-      <c r="M60">
-        <v>1600</v>
-      </c>
-      <c r="N60">
-        <v>6.95</v>
-      </c>
-      <c r="O60">
-        <v>7.15</v>
-      </c>
-      <c r="P60">
-        <v>5900</v>
       </c>
     </row>
     <row r="61">
@@ -3033,47 +3033,47 @@
       <c r="B61" t="str">
         <v>-</v>
       </c>
-      <c r="C61">
-        <v>5.7</v>
-      </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
-      </c>
-      <c r="F61">
-        <v>5.7</v>
-      </c>
-      <c r="G61">
-        <v>5.7</v>
-      </c>
-      <c r="H61">
-        <v>5.7</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <v>3900</v>
-      </c>
-      <c r="L61">
-        <v>22.23</v>
+      <c r="C61" t="str">
+        <v>-</v>
+      </c>
+      <c r="D61" t="str">
+        <v>-</v>
+      </c>
+      <c r="E61" t="str">
+        <v>-</v>
+      </c>
+      <c r="F61" t="str">
+        <v>-</v>
+      </c>
+      <c r="G61" t="str">
+        <v>-</v>
+      </c>
+      <c r="H61" t="str">
+        <v>-</v>
+      </c>
+      <c r="I61" t="str">
+        <v>-</v>
+      </c>
+      <c r="J61" t="str">
+        <v>-</v>
+      </c>
+      <c r="K61" t="str">
+        <v>-</v>
+      </c>
+      <c r="L61" t="str">
+        <v>-</v>
       </c>
       <c r="M61">
-        <v>16000</v>
+        <v>10500</v>
       </c>
       <c r="N61">
         <v>5.65</v>
       </c>
       <c r="O61">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="P61">
-        <v>14400</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="62">
@@ -3084,13 +3084,13 @@
         <v>-</v>
       </c>
       <c r="C62">
-        <v>9.05</v>
+        <v>9.1</v>
       </c>
       <c r="D62">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="E62">
-        <v>0.5555555555555556</v>
+        <v>-1.0869565217391304</v>
       </c>
       <c r="F62">
         <v>9.1</v>
@@ -3099,31 +3099,31 @@
         <v>9.1</v>
       </c>
       <c r="H62">
+        <v>9.1</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>1000</v>
+      </c>
+      <c r="L62">
+        <v>9.1</v>
+      </c>
+      <c r="M62">
+        <v>800</v>
+      </c>
+      <c r="N62">
         <v>9.05</v>
       </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <v>1700</v>
-      </c>
-      <c r="L62">
-        <v>15.435</v>
-      </c>
-      <c r="M62">
-        <v>12200</v>
-      </c>
-      <c r="N62">
-        <v>9</v>
-      </c>
       <c r="O62">
-        <v>9.05</v>
+        <v>9.1</v>
       </c>
       <c r="P62">
-        <v>1300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="63">
@@ -3137,19 +3137,19 @@
         <v>8.05</v>
       </c>
       <c r="D63">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="G63">
         <v>8.05</v>
       </c>
       <c r="H63">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -3158,22 +3158,22 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>4400</v>
+        <v>10900</v>
       </c>
       <c r="L63">
-        <v>35.37</v>
+        <v>86.23</v>
       </c>
       <c r="M63">
-        <v>2100</v>
+        <v>6400</v>
       </c>
       <c r="N63">
+        <v>7.95</v>
+      </c>
+      <c r="O63">
         <v>8.05</v>
       </c>
-      <c r="O63">
-        <v>8.1</v>
-      </c>
       <c r="P63">
-        <v>5300</v>
+        <v>600</v>
       </c>
     </row>
     <row r="64">
@@ -3183,47 +3183,47 @@
       <c r="B64" t="str">
         <v>-</v>
       </c>
-      <c r="C64" t="str">
-        <v>-</v>
-      </c>
-      <c r="D64" t="str">
-        <v>-</v>
-      </c>
-      <c r="E64" t="str">
-        <v>-</v>
-      </c>
-      <c r="F64" t="str">
-        <v>-</v>
-      </c>
-      <c r="G64" t="str">
-        <v>-</v>
-      </c>
-      <c r="H64" t="str">
-        <v>-</v>
-      </c>
-      <c r="I64" t="str">
-        <v>-</v>
-      </c>
-      <c r="J64" t="str">
-        <v>-</v>
-      </c>
-      <c r="K64" t="str">
-        <v>-</v>
-      </c>
-      <c r="L64" t="str">
-        <v>-</v>
+      <c r="C64">
+        <v>1.84</v>
+      </c>
+      <c r="D64">
+        <v>0.04</v>
+      </c>
+      <c r="E64">
+        <v>2.2222222222222223</v>
+      </c>
+      <c r="F64">
+        <v>1.86</v>
+      </c>
+      <c r="G64">
+        <v>1.86</v>
+      </c>
+      <c r="H64">
+        <v>1.84</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>1300</v>
+      </c>
+      <c r="L64">
+        <v>2.394</v>
       </c>
       <c r="M64">
-        <v>10100</v>
+        <v>300</v>
       </c>
       <c r="N64">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="O64">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="P64">
-        <v>100</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="65">
@@ -3234,22 +3234,22 @@
         <v>-</v>
       </c>
       <c r="C65">
-        <v>8.7</v>
+        <v>8.8</v>
       </c>
       <c r="D65">
         <v>0.05</v>
       </c>
       <c r="E65">
-        <v>0.5780346820809249</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="F65">
-        <v>8.6</v>
+        <v>8.65</v>
       </c>
       <c r="G65">
-        <v>8.7</v>
+        <v>8.8</v>
       </c>
       <c r="H65">
-        <v>8.6</v>
+        <v>8.65</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -3258,22 +3258,22 @@
         <v>0</v>
       </c>
       <c r="K65">
-        <v>348300</v>
+        <v>5602</v>
       </c>
       <c r="L65">
-        <v>3028.09</v>
+        <v>49.03245</v>
       </c>
       <c r="M65">
-        <v>120000</v>
+        <v>10600</v>
       </c>
       <c r="N65">
-        <v>8.7</v>
+        <v>8.75</v>
       </c>
       <c r="O65">
-        <v>8.75</v>
+        <v>8.8</v>
       </c>
       <c r="P65">
-        <v>19300</v>
+        <v>64600</v>
       </c>
     </row>
     <row r="66">
@@ -3283,38 +3283,38 @@
       <c r="B66" t="str">
         <v>-</v>
       </c>
-      <c r="C66" t="str">
-        <v>-</v>
-      </c>
-      <c r="D66" t="str">
-        <v>-</v>
-      </c>
-      <c r="E66" t="str">
-        <v>-</v>
-      </c>
-      <c r="F66" t="str">
-        <v>-</v>
-      </c>
-      <c r="G66" t="str">
-        <v>-</v>
-      </c>
-      <c r="H66" t="str">
-        <v>-</v>
-      </c>
-      <c r="I66" t="str">
-        <v>-</v>
-      </c>
-      <c r="J66" t="str">
-        <v>-</v>
-      </c>
-      <c r="K66" t="str">
-        <v>-</v>
-      </c>
-      <c r="L66" t="str">
-        <v>-</v>
+      <c r="C66">
+        <v>22.7</v>
+      </c>
+      <c r="D66">
+        <v>0.1</v>
+      </c>
+      <c r="E66">
+        <v>0.4424778761061947</v>
+      </c>
+      <c r="F66">
+        <v>22.7</v>
+      </c>
+      <c r="G66">
+        <v>22.7</v>
+      </c>
+      <c r="H66">
+        <v>22.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>9105</v>
+      </c>
+      <c r="L66">
+        <v>206.6836</v>
       </c>
       <c r="M66">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="N66">
         <v>22.6</v>
@@ -3323,7 +3323,7 @@
         <v>22.7</v>
       </c>
       <c r="P66">
-        <v>5000</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="67">
@@ -3334,22 +3334,22 @@
         <v>-</v>
       </c>
       <c r="C67">
+        <v>0.91</v>
+      </c>
+      <c r="D67">
+        <v>-0.04</v>
+      </c>
+      <c r="E67">
+        <v>-4.2105263157894735</v>
+      </c>
+      <c r="F67">
+        <v>0.93</v>
+      </c>
+      <c r="G67">
         <v>0.94</v>
       </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-      <c r="E67">
-        <v>0</v>
-      </c>
-      <c r="F67">
-        <v>0.94</v>
-      </c>
-      <c r="G67">
-        <v>0.95</v>
-      </c>
       <c r="H67">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -3358,22 +3358,22 @@
         <v>0</v>
       </c>
       <c r="K67">
-        <v>1300</v>
+        <v>24500</v>
       </c>
       <c r="L67">
-        <v>1.22</v>
+        <v>22.336</v>
       </c>
       <c r="M67">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N67">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="O67">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="P67">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="68">
@@ -3384,22 +3384,22 @@
         <v>-</v>
       </c>
       <c r="C68">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="D68">
-        <v>-0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="E68">
-        <v>-3.9215686274509802</v>
+        <v>-1.0204081632653061</v>
       </c>
       <c r="F68">
         <v>1.95</v>
       </c>
       <c r="G68">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H68">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3411,19 +3411,19 @@
         <v>700</v>
       </c>
       <c r="L68">
-        <v>1.371</v>
+        <v>1.361</v>
       </c>
       <c r="M68">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="N68">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="O68">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="P68">
-        <v>600</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69">
@@ -3433,47 +3433,47 @@
       <c r="B69" t="str">
         <v>-</v>
       </c>
-      <c r="C69" t="str">
-        <v>-</v>
-      </c>
-      <c r="D69" t="str">
-        <v>-</v>
-      </c>
-      <c r="E69" t="str">
-        <v>-</v>
-      </c>
-      <c r="F69" t="str">
-        <v>-</v>
-      </c>
-      <c r="G69" t="str">
-        <v>-</v>
-      </c>
-      <c r="H69" t="str">
-        <v>-</v>
-      </c>
-      <c r="I69" t="str">
-        <v>-</v>
-      </c>
-      <c r="J69" t="str">
-        <v>-</v>
-      </c>
-      <c r="K69" t="str">
-        <v>-</v>
-      </c>
-      <c r="L69" t="str">
-        <v>-</v>
+      <c r="C69">
+        <v>8.8</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>8.85</v>
+      </c>
+      <c r="G69">
+        <v>8.85</v>
+      </c>
+      <c r="H69">
+        <v>8.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>26403</v>
+      </c>
+      <c r="L69">
+        <v>233.05655</v>
       </c>
       <c r="M69">
-        <v>1000</v>
+        <v>2300</v>
       </c>
       <c r="N69">
+        <v>8.75</v>
+      </c>
+      <c r="O69">
         <v>8.8</v>
       </c>
-      <c r="O69">
-        <v>8.85</v>
-      </c>
       <c r="P69">
-        <v>5200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="70">
@@ -3484,16 +3484,16 @@
         <v>-</v>
       </c>
       <c r="C70">
+        <v>8</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
         <v>8.05</v>
-      </c>
-      <c r="D70">
-        <v>0.05</v>
-      </c>
-      <c r="E70">
-        <v>0.625</v>
-      </c>
-      <c r="F70">
-        <v>8</v>
       </c>
       <c r="G70">
         <v>8.05</v>
@@ -3508,13 +3508,13 @@
         <v>0</v>
       </c>
       <c r="K70">
-        <v>347611</v>
+        <v>846450</v>
       </c>
       <c r="L70">
-        <v>2781.65485</v>
+        <v>6771.9452</v>
       </c>
       <c r="M70">
-        <v>83200</v>
+        <v>20300</v>
       </c>
       <c r="N70">
         <v>8</v>
@@ -3523,7 +3523,7 @@
         <v>8.05</v>
       </c>
       <c r="P70">
-        <v>154000</v>
+        <v>131600</v>
       </c>
     </row>
     <row r="71">
@@ -3534,19 +3534,19 @@
         <v>-</v>
       </c>
       <c r="C71">
+        <v>11.6</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>11.6</v>
+      </c>
+      <c r="G71">
         <v>11.7</v>
-      </c>
-      <c r="D71">
-        <v>-0.1</v>
-      </c>
-      <c r="E71">
-        <v>-0.847457627118644</v>
-      </c>
-      <c r="F71">
-        <v>11.8</v>
-      </c>
-      <c r="G71">
-        <v>11.8</v>
       </c>
       <c r="H71">
         <v>11.6</v>
@@ -3558,22 +3558,22 @@
         <v>0</v>
       </c>
       <c r="K71">
-        <v>426705</v>
+        <v>484312</v>
       </c>
       <c r="L71">
-        <v>5004.128</v>
+        <v>5621.8992</v>
       </c>
       <c r="M71">
-        <v>71600</v>
+        <v>53200</v>
       </c>
       <c r="N71">
+        <v>11.6</v>
+      </c>
+      <c r="O71">
         <v>11.7</v>
       </c>
-      <c r="O71">
-        <v>11.8</v>
-      </c>
       <c r="P71">
-        <v>308200</v>
+        <v>183000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StockQuotation (7).xlsx
+++ b/Excel/StockQuotation (7).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>07/02/23 23:30:28</v>
+        <v>08/02/23 20:06:34</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>161.33</v>
+        <v>160.92</v>
       </c>
       <c r="B7" t="str">
-        <v>-0.24 (-0.1485%)</v>
+        <v>-0.41 (-0.2541%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>161.89</v>
+        <v>161.44</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>160.8</v>
+        <v>160.43</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>11943384</v>
+        <v>12298701</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>141280206.7</v>
+        <v>155048228.45</v>
       </c>
     </row>
     <row r="9">
@@ -546,10 +546,10 @@
         <v>5.5</v>
       </c>
       <c r="G11">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="H11">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -558,13 +558,13 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>379547</v>
+        <v>96005</v>
       </c>
       <c r="L11">
-        <v>2082.2345</v>
+        <v>519.7395</v>
       </c>
       <c r="M11">
-        <v>66000</v>
+        <v>72600</v>
       </c>
       <c r="N11">
         <v>5.4</v>
@@ -573,7 +573,7 @@
         <v>5.45</v>
       </c>
       <c r="P11">
-        <v>49700</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="12">
@@ -587,16 +587,16 @@
         <v>12.3</v>
       </c>
       <c r="D12">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>-0.8064516129032258</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="G12">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="H12">
         <v>12.3</v>
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>122600</v>
+        <v>291801</v>
       </c>
       <c r="L12">
-        <v>1508.11</v>
+        <v>3589.1522999999997</v>
       </c>
       <c r="M12">
-        <v>239200</v>
+        <v>343400</v>
       </c>
       <c r="N12">
+        <v>12.2</v>
+      </c>
+      <c r="O12">
         <v>12.3</v>
       </c>
-      <c r="O12">
-        <v>12.4</v>
-      </c>
       <c r="P12">
-        <v>81500</v>
+        <v>427900</v>
       </c>
     </row>
     <row r="13">
@@ -649,7 +649,7 @@
         <v>7.45</v>
       </c>
       <c r="H13">
-        <v>7.35</v>
+        <v>7.4</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -658,22 +658,22 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>187400</v>
+        <v>168000</v>
       </c>
       <c r="L13">
-        <v>1386.47</v>
+        <v>1251.43</v>
       </c>
       <c r="M13">
-        <v>121800</v>
+        <v>164700</v>
       </c>
       <c r="N13">
-        <v>7.35</v>
+        <v>7.4</v>
       </c>
       <c r="O13">
-        <v>7.4</v>
+        <v>7.45</v>
       </c>
       <c r="P13">
-        <v>9800</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         <v>6.85</v>
       </c>
       <c r="G14">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="H14">
         <v>6.8</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>283475</v>
+        <v>91500</v>
       </c>
       <c r="L14">
-        <v>1940.41375</v>
+        <v>625.405</v>
       </c>
       <c r="M14">
-        <v>39800</v>
+        <v>500</v>
       </c>
       <c r="N14">
         <v>6.85</v>
@@ -723,7 +723,7 @@
         <v>6.9</v>
       </c>
       <c r="P14">
-        <v>9500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="15">
@@ -737,16 +737,16 @@
         <v>9.95</v>
       </c>
       <c r="D15">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>0.5050505050505051</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>9.95</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>9.95</v>
       </c>
       <c r="H15">
         <v>9.95</v>
@@ -758,13 +758,13 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>31601</v>
+        <v>13700</v>
       </c>
       <c r="L15">
-        <v>314.457</v>
+        <v>136.315</v>
       </c>
       <c r="M15">
-        <v>110000</v>
+        <v>166500</v>
       </c>
       <c r="N15">
         <v>9.9</v>
@@ -773,7 +773,7 @@
         <v>9.95</v>
       </c>
       <c r="P15">
-        <v>365900</v>
+        <v>687800</v>
       </c>
     </row>
     <row r="16">
@@ -808,13 +808,13 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>1366768</v>
+        <v>1617306</v>
       </c>
       <c r="L16">
-        <v>14899.828</v>
+        <v>17634.2458</v>
       </c>
       <c r="M16">
-        <v>878500</v>
+        <v>57700</v>
       </c>
       <c r="N16">
         <v>10.9</v>
@@ -823,7 +823,7 @@
         <v>11</v>
       </c>
       <c r="P16">
-        <v>1906500</v>
+        <v>1160300</v>
       </c>
     </row>
     <row r="17">
@@ -833,23 +833,23 @@
       <c r="B17" t="str">
         <v>-</v>
       </c>
-      <c r="C17">
-        <v>10.5</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>10.4</v>
-      </c>
-      <c r="G17">
-        <v>10.5</v>
-      </c>
-      <c r="H17">
-        <v>10.4</v>
+      <c r="C17" t="str">
+        <v>-</v>
+      </c>
+      <c r="D17" t="str">
+        <v>-</v>
+      </c>
+      <c r="E17" t="str">
+        <v>-</v>
+      </c>
+      <c r="F17" t="str">
+        <v>-</v>
+      </c>
+      <c r="G17" t="str">
+        <v>-</v>
+      </c>
+      <c r="H17" t="str">
+        <v>-</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -858,13 +858,13 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>203</v>
+        <v>1</v>
       </c>
       <c r="L17">
-        <v>2.1215</v>
+        <v>0.0104</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>5300</v>
       </c>
       <c r="N17">
         <v>10.4</v>
@@ -873,7 +873,7 @@
         <v>10.5</v>
       </c>
       <c r="P17">
-        <v>6200</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="18">
@@ -893,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>8.45</v>
+        <v>8.4</v>
       </c>
       <c r="G18">
         <v>8.45</v>
@@ -908,22 +908,22 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>12902</v>
+        <v>489602</v>
       </c>
       <c r="L18">
-        <v>108.1569</v>
+        <v>4112.6918</v>
       </c>
       <c r="M18">
-        <v>2900</v>
+        <v>6100</v>
       </c>
       <c r="N18">
+        <v>8.35</v>
+      </c>
+      <c r="O18">
         <v>8.4</v>
       </c>
-      <c r="O18">
-        <v>8.45</v>
-      </c>
       <c r="P18">
-        <v>14600</v>
+        <v>131700</v>
       </c>
     </row>
     <row r="19">
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="G19">
         <v>11.7</v>
@@ -958,13 +958,13 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>165600</v>
+        <v>130446</v>
       </c>
       <c r="L19">
-        <v>1935.49</v>
+        <v>1524.5782</v>
       </c>
       <c r="M19">
-        <v>226900</v>
+        <v>322400</v>
       </c>
       <c r="N19">
         <v>11.6</v>
@@ -973,7 +973,7 @@
         <v>11.7</v>
       </c>
       <c r="P19">
-        <v>291600</v>
+        <v>258200</v>
       </c>
     </row>
     <row r="20">
@@ -984,22 +984,22 @@
         <v>-</v>
       </c>
       <c r="C20">
+        <v>18.4</v>
+      </c>
+      <c r="D20">
+        <v>-0.1</v>
+      </c>
+      <c r="E20">
+        <v>-0.5405405405405406</v>
+      </c>
+      <c r="F20">
         <v>18.5</v>
       </c>
-      <c r="D20">
-        <v>-0.2</v>
-      </c>
-      <c r="E20">
-        <v>-1.0695187165775402</v>
-      </c>
-      <c r="F20">
-        <v>18.7</v>
-      </c>
       <c r="G20">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="H20">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1008,13 +1008,13 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>2548603</v>
+        <v>3746543</v>
       </c>
       <c r="L20">
-        <v>46882.963200000006</v>
+        <v>68769.71579999999</v>
       </c>
       <c r="M20">
-        <v>35600</v>
+        <v>23200</v>
       </c>
       <c r="N20">
         <v>18.4</v>
@@ -1023,7 +1023,7 @@
         <v>18.5</v>
       </c>
       <c r="P20">
-        <v>379300</v>
+        <v>580500</v>
       </c>
     </row>
     <row r="21">
@@ -1037,19 +1037,19 @@
         <v>7.7</v>
       </c>
       <c r="D21">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>2.6666666666666665</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>7.55</v>
+        <v>7.7</v>
       </c>
       <c r="G21">
-        <v>7.8</v>
+        <v>7.75</v>
       </c>
       <c r="H21">
-        <v>7.55</v>
+        <v>7.65</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1058,22 +1058,22 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>693623</v>
+        <v>800969</v>
       </c>
       <c r="L21">
-        <v>5312.93745</v>
+        <v>6167.3191</v>
       </c>
       <c r="M21">
-        <v>800</v>
+        <v>18200</v>
       </c>
       <c r="N21">
-        <v>7.65</v>
+        <v>7.7</v>
       </c>
       <c r="O21">
-        <v>7.7</v>
+        <v>7.75</v>
       </c>
       <c r="P21">
-        <v>103600</v>
+        <v>114200</v>
       </c>
     </row>
     <row r="22">
@@ -1087,19 +1087,19 @@
         <v>5.35</v>
       </c>
       <c r="D22">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>0.9433962264150944</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="G22">
         <v>5.35</v>
       </c>
       <c r="H22">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1108,22 +1108,22 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>74500</v>
       </c>
       <c r="L22">
-        <v>0.535</v>
+        <v>392.835</v>
       </c>
       <c r="M22">
-        <v>14300</v>
+        <v>89400</v>
       </c>
       <c r="N22">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="O22">
         <v>5.35</v>
       </c>
       <c r="P22">
-        <v>23400</v>
+        <v>23300</v>
       </c>
     </row>
     <row r="23">
@@ -1134,19 +1134,19 @@
         <v>-</v>
       </c>
       <c r="C23">
+        <v>6.25</v>
+      </c>
+      <c r="D23">
+        <v>0.05</v>
+      </c>
+      <c r="E23">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="F23">
         <v>6.2</v>
       </c>
-      <c r="D23">
-        <v>-0.05</v>
-      </c>
-      <c r="E23">
-        <v>-0.8</v>
-      </c>
-      <c r="F23">
-        <v>6.25</v>
-      </c>
       <c r="G23">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="H23">
         <v>6.2</v>
@@ -1158,13 +1158,13 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>31005</v>
+        <v>21100</v>
       </c>
       <c r="L23">
-        <v>192.38629999999998</v>
+        <v>131.235</v>
       </c>
       <c r="M23">
-        <v>7000</v>
+        <v>67900</v>
       </c>
       <c r="N23">
         <v>6.2</v>
@@ -1173,7 +1173,7 @@
         <v>6.25</v>
       </c>
       <c r="P23">
-        <v>500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="24">
@@ -1184,19 +1184,19 @@
         <v>-</v>
       </c>
       <c r="C24">
-        <v>4.34</v>
+        <v>4.28</v>
       </c>
       <c r="D24">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="E24">
-        <v>0.9302325581395349</v>
+        <v>-1.3824884792626728</v>
       </c>
       <c r="F24">
-        <v>4.28</v>
+        <v>4.32</v>
       </c>
       <c r="G24">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="H24">
         <v>4.28</v>
@@ -1208,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>398900</v>
+        <v>95200</v>
       </c>
       <c r="L24">
-        <v>1713.952</v>
+        <v>409.154</v>
       </c>
       <c r="M24">
-        <v>162400</v>
+        <v>121500</v>
       </c>
       <c r="N24">
         <v>4.28</v>
       </c>
       <c r="O24">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="P24">
-        <v>17300</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="25">
@@ -1234,46 +1234,46 @@
         <v>-</v>
       </c>
       <c r="C25">
+        <v>11.6</v>
+      </c>
+      <c r="D25">
+        <v>-0.1</v>
+      </c>
+      <c r="E25">
+        <v>-0.8547008547008547</v>
+      </c>
+      <c r="F25">
+        <v>11.8</v>
+      </c>
+      <c r="G25">
+        <v>11.8</v>
+      </c>
+      <c r="H25">
+        <v>11.6</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>367444</v>
+      </c>
+      <c r="L25">
+        <v>4276.651400000001</v>
+      </c>
+      <c r="M25">
+        <v>44300</v>
+      </c>
+      <c r="N25">
+        <v>11.6</v>
+      </c>
+      <c r="O25">
         <v>11.7</v>
       </c>
-      <c r="D25">
-        <v>-0.2</v>
-      </c>
-      <c r="E25">
-        <v>-1.680672268907563</v>
-      </c>
-      <c r="F25">
-        <v>11.9</v>
-      </c>
-      <c r="G25">
-        <v>11.9</v>
-      </c>
-      <c r="H25">
-        <v>11.7</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>196402</v>
-      </c>
-      <c r="L25">
-        <v>2314.854</v>
-      </c>
-      <c r="M25">
-        <v>79900</v>
-      </c>
-      <c r="N25">
-        <v>11.7</v>
-      </c>
-      <c r="O25">
-        <v>11.8</v>
-      </c>
       <c r="P25">
-        <v>167800</v>
+        <v>189700</v>
       </c>
     </row>
     <row r="26">
@@ -1284,13 +1284,13 @@
         <v>-</v>
       </c>
       <c r="C26">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="F26">
         <v>15</v>
@@ -1308,13 +1308,13 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>195600</v>
+        <v>23000</v>
       </c>
       <c r="L26">
-        <v>2930.42</v>
+        <v>342.71</v>
       </c>
       <c r="M26">
-        <v>47700</v>
+        <v>49000</v>
       </c>
       <c r="N26">
         <v>14.9</v>
@@ -1323,7 +1323,7 @@
         <v>15</v>
       </c>
       <c r="P26">
-        <v>48600</v>
+        <v>56300</v>
       </c>
     </row>
     <row r="27">
@@ -1337,16 +1337,16 @@
         <v>8.6</v>
       </c>
       <c r="D27">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>0.5847953216374269</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>8.6</v>
+        <v>8.65</v>
       </c>
       <c r="G27">
-        <v>8.6</v>
+        <v>8.65</v>
       </c>
       <c r="H27">
         <v>8.6</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>5000</v>
+        <v>301</v>
       </c>
       <c r="L27">
-        <v>43</v>
+        <v>2.5936999999999997</v>
       </c>
       <c r="M27">
-        <v>5700</v>
+        <v>26100</v>
       </c>
       <c r="N27">
         <v>8.5</v>
@@ -1373,7 +1373,7 @@
         <v>8.6</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>174600</v>
       </c>
     </row>
     <row r="28">
@@ -1384,22 +1384,22 @@
         <v>-</v>
       </c>
       <c r="C28">
-        <v>9.8</v>
+        <v>9.85</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="F28">
-        <v>9.8</v>
+        <v>9.85</v>
       </c>
       <c r="G28">
         <v>9.85</v>
       </c>
       <c r="H28">
-        <v>9.8</v>
+        <v>9.85</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1408,13 +1408,13 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>122400</v>
+        <v>8800</v>
       </c>
       <c r="L28">
-        <v>1202.06</v>
+        <v>86.68</v>
       </c>
       <c r="M28">
-        <v>1200</v>
+        <v>13500</v>
       </c>
       <c r="N28">
         <v>9.8</v>
@@ -1423,7 +1423,7 @@
         <v>9.85</v>
       </c>
       <c r="P28">
-        <v>12200</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29">
@@ -1434,22 +1434,22 @@
         <v>-</v>
       </c>
       <c r="C29">
+        <v>9.75</v>
+      </c>
+      <c r="D29">
+        <v>-0.05</v>
+      </c>
+      <c r="E29">
+        <v>-0.5102040816326531</v>
+      </c>
+      <c r="F29">
+        <v>9.75</v>
+      </c>
+      <c r="G29">
         <v>9.8</v>
       </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>9.8</v>
-      </c>
-      <c r="G29">
-        <v>9.85</v>
-      </c>
       <c r="H29">
-        <v>9.8</v>
+        <v>9.55</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1458,22 +1458,22 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>417700</v>
+        <v>375806</v>
       </c>
       <c r="L29">
-        <v>4095.57</v>
+        <v>3653.7738</v>
       </c>
       <c r="M29">
-        <v>23800</v>
+        <v>7100</v>
       </c>
       <c r="N29">
+        <v>9.65</v>
+      </c>
+      <c r="O29">
         <v>9.75</v>
       </c>
-      <c r="O29">
-        <v>9.8</v>
-      </c>
       <c r="P29">
-        <v>26000</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="30">
@@ -1484,13 +1484,13 @@
         <v>-</v>
       </c>
       <c r="C30">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>0.41841004184100417</v>
       </c>
       <c r="F30">
         <v>4.8</v>
@@ -1508,22 +1508,22 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>8800</v>
+        <v>13500</v>
       </c>
       <c r="L30">
-        <v>42.084</v>
+        <v>64.56</v>
       </c>
       <c r="M30">
-        <v>17200</v>
+        <v>13300</v>
       </c>
       <c r="N30">
-        <v>4.78</v>
+        <v>4.76</v>
       </c>
       <c r="O30">
         <v>4.8</v>
       </c>
       <c r="P30">
-        <v>5000</v>
+        <v>12800</v>
       </c>
     </row>
     <row r="31">
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="G31">
         <v>10.3</v>
@@ -1558,13 +1558,13 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>40300</v>
+        <v>11100</v>
       </c>
       <c r="L31">
-        <v>411.07</v>
+        <v>113.33</v>
       </c>
       <c r="M31">
-        <v>104300</v>
+        <v>55600</v>
       </c>
       <c r="N31">
         <v>10.2</v>
@@ -1573,7 +1573,7 @@
         <v>10.3</v>
       </c>
       <c r="P31">
-        <v>95900</v>
+        <v>109700</v>
       </c>
     </row>
     <row r="32">
@@ -1584,16 +1584,16 @@
         <v>-</v>
       </c>
       <c r="C32">
+        <v>13.7</v>
+      </c>
+      <c r="D32">
+        <v>-0.1</v>
+      </c>
+      <c r="E32">
+        <v>-0.7246376811594203</v>
+      </c>
+      <c r="F32">
         <v>13.8</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>13.7</v>
       </c>
       <c r="G32">
         <v>13.8</v>
@@ -1608,22 +1608,22 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>911982</v>
+        <v>517631</v>
       </c>
       <c r="L32">
-        <v>12508.3183</v>
+        <v>7122.865900000001</v>
       </c>
       <c r="M32">
-        <v>65900</v>
+        <v>266600</v>
       </c>
       <c r="N32">
+        <v>13.6</v>
+      </c>
+      <c r="O32">
         <v>13.7</v>
       </c>
-      <c r="O32">
-        <v>13.8</v>
-      </c>
       <c r="P32">
-        <v>265300</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="33">
@@ -1634,19 +1634,19 @@
         <v>-</v>
       </c>
       <c r="C33">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="D33">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="E33">
-        <v>0.8620689655172413</v>
+        <v>-0.8547008547008547</v>
       </c>
       <c r="F33">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="G33">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="H33">
         <v>11.6</v>
@@ -1658,22 +1658,22 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>88906</v>
+        <v>304600</v>
       </c>
       <c r="L33">
-        <v>1035.4102</v>
+        <v>3533.36</v>
       </c>
       <c r="M33">
-        <v>36900</v>
+        <v>77000</v>
       </c>
       <c r="N33">
+        <v>11.5</v>
+      </c>
+      <c r="O33">
         <v>11.6</v>
       </c>
-      <c r="O33">
-        <v>11.7</v>
-      </c>
       <c r="P33">
-        <v>61600</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="34">
@@ -1683,47 +1683,47 @@
       <c r="B34" t="str">
         <v>-</v>
       </c>
-      <c r="C34" t="str">
-        <v>-</v>
-      </c>
-      <c r="D34" t="str">
-        <v>-</v>
-      </c>
-      <c r="E34" t="str">
-        <v>-</v>
-      </c>
-      <c r="F34" t="str">
-        <v>-</v>
-      </c>
-      <c r="G34" t="str">
-        <v>-</v>
-      </c>
-      <c r="H34" t="str">
-        <v>-</v>
-      </c>
-      <c r="I34" t="str">
-        <v>-</v>
-      </c>
-      <c r="J34" t="str">
-        <v>-</v>
-      </c>
-      <c r="K34" t="str">
-        <v>-</v>
-      </c>
-      <c r="L34" t="str">
-        <v>-</v>
+      <c r="C34">
+        <v>5.05</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>5.05</v>
+      </c>
+      <c r="G34">
+        <v>5.1</v>
+      </c>
+      <c r="H34">
+        <v>5.05</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>12011</v>
+      </c>
+      <c r="L34">
+        <v>60.7061</v>
       </c>
       <c r="M34">
-        <v>13000</v>
+        <v>100</v>
       </c>
       <c r="N34">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="O34">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="P34">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -1734,23 +1734,23 @@
         <v>-</v>
       </c>
       <c r="C35">
-        <v>8.85</v>
+        <v>8.95</v>
       </c>
       <c r="D35">
         <v>0.1</v>
       </c>
       <c r="E35">
-        <v>1.1428571428571428</v>
+        <v>1.1299435028248588</v>
       </c>
       <c r="F35">
-        <v>8.75</v>
+        <v>8.85</v>
       </c>
       <c r="G35">
+        <v>8.95</v>
+      </c>
+      <c r="H35">
         <v>8.85</v>
       </c>
-      <c r="H35">
-        <v>8.75</v>
-      </c>
       <c r="I35">
         <v>0</v>
       </c>
@@ -1758,22 +1758,22 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>69300</v>
+        <v>35510</v>
       </c>
       <c r="L35">
-        <v>606.66</v>
+        <v>315.9785</v>
       </c>
       <c r="M35">
-        <v>8000</v>
+        <v>4400</v>
       </c>
       <c r="N35">
-        <v>8.75</v>
+        <v>8.85</v>
       </c>
       <c r="O35">
-        <v>8.85</v>
+        <v>8.95</v>
       </c>
       <c r="P35">
-        <v>2100</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="36">
@@ -1784,22 +1784,22 @@
         <v>-</v>
       </c>
       <c r="C36">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="D36">
         <v>-0.1</v>
       </c>
       <c r="E36">
-        <v>-0.7299270072992701</v>
+        <v>-0.7352941176470589</v>
       </c>
       <c r="F36">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="G36">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="H36">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1808,13 +1808,13 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>352500</v>
+        <v>224000</v>
       </c>
       <c r="L36">
-        <v>4830.33</v>
+        <v>3049.79</v>
       </c>
       <c r="M36">
-        <v>131000</v>
+        <v>109200</v>
       </c>
       <c r="N36">
         <v>13.5</v>
@@ -1823,7 +1823,7 @@
         <v>13.6</v>
       </c>
       <c r="P36">
-        <v>334600</v>
+        <v>198500</v>
       </c>
     </row>
     <row r="37">
@@ -1834,22 +1834,22 @@
         <v>-</v>
       </c>
       <c r="C37">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="F37">
         <v>6.6</v>
       </c>
       <c r="G37">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="H37">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1858,22 +1858,22 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>18300</v>
+        <v>33700</v>
       </c>
       <c r="L37">
-        <v>120.78</v>
+        <v>222.245</v>
       </c>
       <c r="M37">
-        <v>5600</v>
+        <v>6800</v>
       </c>
       <c r="N37">
         <v>6.55</v>
       </c>
       <c r="O37">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="P37">
-        <v>700</v>
+        <v>31600</v>
       </c>
     </row>
     <row r="38">
@@ -1884,46 +1884,46 @@
         <v>-</v>
       </c>
       <c r="C38">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>-1.6528925619834711</v>
       </c>
       <c r="F38">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="G38">
         <v>12.1</v>
       </c>
       <c r="H38">
+        <v>11.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>40900</v>
+      </c>
+      <c r="L38">
+        <v>489.55</v>
+      </c>
+      <c r="M38">
+        <v>1900</v>
+      </c>
+      <c r="N38">
+        <v>11.9</v>
+      </c>
+      <c r="O38">
         <v>12.1</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>3252</v>
-      </c>
-      <c r="L38">
-        <v>39.349199999999996</v>
-      </c>
-      <c r="M38">
-        <v>1300</v>
-      </c>
-      <c r="N38">
-        <v>12.1</v>
-      </c>
-      <c r="O38">
-        <v>12.3</v>
-      </c>
       <c r="P38">
-        <v>9500</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="39">
@@ -1934,22 +1934,22 @@
         <v>-</v>
       </c>
       <c r="C39">
+        <v>14.1</v>
+      </c>
+      <c r="D39">
+        <v>-0.1</v>
+      </c>
+      <c r="E39">
+        <v>-0.704225352112676</v>
+      </c>
+      <c r="F39">
         <v>14.2</v>
-      </c>
-      <c r="D39">
-        <v>0.2</v>
-      </c>
-      <c r="E39">
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="F39">
-        <v>14</v>
       </c>
       <c r="G39">
         <v>14.3</v>
       </c>
       <c r="H39">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -1958,22 +1958,22 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>366099</v>
+        <v>91010</v>
       </c>
       <c r="L39">
-        <v>5189.57</v>
+        <v>1288.702</v>
       </c>
       <c r="M39">
-        <v>1400</v>
+        <v>110600</v>
       </c>
       <c r="N39">
+        <v>14.1</v>
+      </c>
+      <c r="O39">
         <v>14.2</v>
       </c>
-      <c r="O39">
-        <v>14.3</v>
-      </c>
       <c r="P39">
-        <v>356800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="40">
@@ -1984,46 +1984,46 @@
         <v>-</v>
       </c>
       <c r="C40">
-        <v>7.55</v>
+        <v>7.5</v>
       </c>
       <c r="D40">
         <v>-0.05</v>
       </c>
       <c r="E40">
-        <v>-0.6578947368421053</v>
+        <v>-0.6622516556291391</v>
       </c>
       <c r="F40">
+        <v>7.5</v>
+      </c>
+      <c r="G40">
+        <v>7.5</v>
+      </c>
+      <c r="H40">
+        <v>7.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>31000</v>
+      </c>
+      <c r="L40">
+        <v>232.5</v>
+      </c>
+      <c r="M40">
+        <v>18700</v>
+      </c>
+      <c r="N40">
         <v>7.45</v>
       </c>
-      <c r="G40">
-        <v>7.55</v>
-      </c>
-      <c r="H40">
-        <v>7.45</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>46700</v>
-      </c>
-      <c r="L40">
-        <v>350.72</v>
-      </c>
-      <c r="M40">
-        <v>5000</v>
-      </c>
-      <c r="N40">
+      <c r="O40">
         <v>7.5</v>
       </c>
-      <c r="O40">
-        <v>7.55</v>
-      </c>
       <c r="P40">
-        <v>8800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="41">
@@ -2058,22 +2058,22 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>1015</v>
+        <v>9100</v>
       </c>
       <c r="L41">
-        <v>7.5095</v>
+        <v>67.34</v>
       </c>
       <c r="M41">
-        <v>5800</v>
+        <v>300300</v>
       </c>
       <c r="N41">
-        <v>7.4</v>
+        <v>7.35</v>
       </c>
       <c r="O41">
         <v>7.45</v>
       </c>
       <c r="P41">
-        <v>14000</v>
+        <v>10100</v>
       </c>
     </row>
     <row r="42">
@@ -2084,22 +2084,22 @@
         <v>-</v>
       </c>
       <c r="C42">
+        <v>4.88</v>
+      </c>
+      <c r="D42">
+        <v>0.12</v>
+      </c>
+      <c r="E42">
+        <v>2.5210084033613445</v>
+      </c>
+      <c r="F42">
         <v>4.76</v>
       </c>
-      <c r="D42">
-        <v>-0.1</v>
-      </c>
-      <c r="E42">
-        <v>-2.05761316872428</v>
-      </c>
-      <c r="F42">
-        <v>4.46</v>
-      </c>
       <c r="G42">
-        <v>4.8</v>
+        <v>4.88</v>
       </c>
       <c r="H42">
-        <v>4.46</v>
+        <v>4.76</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2108,22 +2108,22 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>6200</v>
+        <v>1200</v>
       </c>
       <c r="L42">
-        <v>29.216</v>
+        <v>5.724</v>
       </c>
       <c r="M42">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="N42">
         <v>4.5</v>
       </c>
       <c r="O42">
-        <v>4.78</v>
+        <v>4.84</v>
       </c>
       <c r="P42">
-        <v>2200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">
@@ -2133,38 +2133,38 @@
       <c r="B43" t="str">
         <v>-</v>
       </c>
-      <c r="C43">
-        <v>6.05</v>
-      </c>
-      <c r="D43">
-        <v>-0.05</v>
-      </c>
-      <c r="E43">
-        <v>-0.819672131147541</v>
-      </c>
-      <c r="F43">
-        <v>6.05</v>
-      </c>
-      <c r="G43">
-        <v>6.15</v>
-      </c>
-      <c r="H43">
-        <v>6.05</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>3600</v>
-      </c>
-      <c r="L43">
-        <v>21.88</v>
+      <c r="C43" t="str">
+        <v>-</v>
+      </c>
+      <c r="D43" t="str">
+        <v>-</v>
+      </c>
+      <c r="E43" t="str">
+        <v>-</v>
+      </c>
+      <c r="F43" t="str">
+        <v>-</v>
+      </c>
+      <c r="G43" t="str">
+        <v>-</v>
+      </c>
+      <c r="H43" t="str">
+        <v>-</v>
+      </c>
+      <c r="I43" t="str">
+        <v>-</v>
+      </c>
+      <c r="J43" t="str">
+        <v>-</v>
+      </c>
+      <c r="K43" t="str">
+        <v>-</v>
+      </c>
+      <c r="L43" t="str">
+        <v>-</v>
       </c>
       <c r="M43">
-        <v>2500</v>
+        <v>300</v>
       </c>
       <c r="N43">
         <v>6.05</v>
@@ -2173,7 +2173,7 @@
         <v>6.15</v>
       </c>
       <c r="P43">
-        <v>14100</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="44">
@@ -2214,10 +2214,10 @@
         <v>-</v>
       </c>
       <c r="M44">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N44">
-        <v>12.3</v>
+        <v>11.2</v>
       </c>
       <c r="O44">
         <v>18.7</v>
@@ -2237,19 +2237,19 @@
         <v>1.73</v>
       </c>
       <c r="D45">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>-0.5747126436781609</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G45">
         <v>1.75</v>
       </c>
       <c r="H45">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2258,22 +2258,22 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>42700</v>
+        <v>14600</v>
       </c>
       <c r="L45">
-        <v>73.722</v>
+        <v>25.234</v>
       </c>
       <c r="M45">
-        <v>15500</v>
+        <v>600</v>
       </c>
       <c r="N45">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="O45">
         <v>1.74</v>
       </c>
       <c r="P45">
-        <v>5000</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="46">
@@ -2284,16 +2284,16 @@
         <v>-</v>
       </c>
       <c r="C46">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="D46">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E46">
-        <v>0.8333333333333334</v>
+        <v>-0.8264462809917356</v>
       </c>
       <c r="F46">
-        <v>6.05</v>
+        <v>5.95</v>
       </c>
       <c r="G46">
         <v>6.05</v>
@@ -2308,22 +2308,22 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>32711</v>
+        <v>37902</v>
       </c>
       <c r="L46">
-        <v>196.171</v>
+        <v>227.65705</v>
       </c>
       <c r="M46">
-        <v>19000</v>
+        <v>10500</v>
       </c>
       <c r="N46">
         <v>5.95</v>
       </c>
       <c r="O46">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="P46">
-        <v>5300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="47">
@@ -2333,47 +2333,47 @@
       <c r="B47" t="str">
         <v>-</v>
       </c>
-      <c r="C47" t="str">
-        <v>-</v>
-      </c>
-      <c r="D47" t="str">
-        <v>-</v>
-      </c>
-      <c r="E47" t="str">
-        <v>-</v>
-      </c>
-      <c r="F47" t="str">
-        <v>-</v>
-      </c>
-      <c r="G47" t="str">
-        <v>-</v>
-      </c>
-      <c r="H47" t="str">
-        <v>-</v>
-      </c>
-      <c r="I47" t="str">
-        <v>-</v>
-      </c>
-      <c r="J47" t="str">
-        <v>-</v>
-      </c>
-      <c r="K47" t="str">
-        <v>-</v>
-      </c>
-      <c r="L47" t="str">
-        <v>-</v>
+      <c r="C47">
+        <v>1.65</v>
+      </c>
+      <c r="D47">
+        <v>-0.05</v>
+      </c>
+      <c r="E47">
+        <v>-2.9411764705882355</v>
+      </c>
+      <c r="F47">
+        <v>1.65</v>
+      </c>
+      <c r="G47">
+        <v>1.65</v>
+      </c>
+      <c r="H47">
+        <v>1.65</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>500</v>
+      </c>
+      <c r="L47">
+        <v>0.825</v>
       </c>
       <c r="M47">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="N47">
         <v>1.64</v>
       </c>
       <c r="O47">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="P47">
-        <v>15200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="48">
@@ -2414,7 +2414,7 @@
         <v>-</v>
       </c>
       <c r="M48">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="N48">
         <v>4.92</v>
@@ -2433,38 +2433,38 @@
       <c r="B49" t="str">
         <v>-</v>
       </c>
-      <c r="C49">
-        <v>2.84</v>
-      </c>
-      <c r="D49">
-        <v>0.02</v>
-      </c>
-      <c r="E49">
-        <v>0.7092198581560284</v>
-      </c>
-      <c r="F49">
-        <v>2.84</v>
-      </c>
-      <c r="G49">
-        <v>2.84</v>
-      </c>
-      <c r="H49">
-        <v>2.84</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>100</v>
-      </c>
-      <c r="L49">
-        <v>0.284</v>
+      <c r="C49" t="str">
+        <v>-</v>
+      </c>
+      <c r="D49" t="str">
+        <v>-</v>
+      </c>
+      <c r="E49" t="str">
+        <v>-</v>
+      </c>
+      <c r="F49" t="str">
+        <v>-</v>
+      </c>
+      <c r="G49" t="str">
+        <v>-</v>
+      </c>
+      <c r="H49" t="str">
+        <v>-</v>
+      </c>
+      <c r="I49" t="str">
+        <v>-</v>
+      </c>
+      <c r="J49" t="str">
+        <v>-</v>
+      </c>
+      <c r="K49" t="str">
+        <v>-</v>
+      </c>
+      <c r="L49" t="str">
+        <v>-</v>
       </c>
       <c r="M49">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="N49">
         <v>2.82</v>
@@ -2493,7 +2493,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="G50">
         <v>11.7</v>
@@ -2508,13 +2508,13 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>435600</v>
+        <v>839741</v>
       </c>
       <c r="L50">
-        <v>5095.62</v>
+        <v>9805.4797</v>
       </c>
       <c r="M50">
-        <v>204600</v>
+        <v>144700</v>
       </c>
       <c r="N50">
         <v>11.6</v>
@@ -2523,7 +2523,7 @@
         <v>11.7</v>
       </c>
       <c r="P50">
-        <v>399400</v>
+        <v>577700</v>
       </c>
     </row>
     <row r="51">
@@ -2534,19 +2534,19 @@
         <v>-</v>
       </c>
       <c r="C51">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>-0.8695652173913043</v>
       </c>
       <c r="F51">
         <v>11.4</v>
       </c>
       <c r="G51">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="H51">
         <v>11.4</v>
@@ -2558,13 +2558,13 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>63300</v>
+        <v>21010</v>
       </c>
       <c r="L51">
-        <v>721.95</v>
+        <v>239.524</v>
       </c>
       <c r="M51">
-        <v>25100</v>
+        <v>7100</v>
       </c>
       <c r="N51">
         <v>11.4</v>
@@ -2573,7 +2573,7 @@
         <v>11.5</v>
       </c>
       <c r="P51">
-        <v>46700</v>
+        <v>32900</v>
       </c>
     </row>
     <row r="52">
@@ -2584,22 +2584,22 @@
         <v>-</v>
       </c>
       <c r="C52">
-        <v>9.6</v>
+        <v>9.65</v>
       </c>
       <c r="D52">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E52">
-        <v>-1.0309278350515463</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="F52">
-        <v>9.6</v>
+        <v>9.55</v>
       </c>
       <c r="G52">
-        <v>9.65</v>
+        <v>9.7</v>
       </c>
       <c r="H52">
-        <v>9.55</v>
+        <v>9.5</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2608,22 +2608,22 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>585855</v>
+        <v>164700</v>
       </c>
       <c r="L52">
-        <v>5619.803</v>
+        <v>1574.155</v>
       </c>
       <c r="M52">
-        <v>2200</v>
+        <v>6000</v>
       </c>
       <c r="N52">
         <v>9.55</v>
       </c>
       <c r="O52">
-        <v>9.6</v>
+        <v>9.65</v>
       </c>
       <c r="P52">
-        <v>67500</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="53">
@@ -2634,46 +2634,46 @@
         <v>-</v>
       </c>
       <c r="C53">
+        <v>6.5</v>
+      </c>
+      <c r="D53">
+        <v>-0.05</v>
+      </c>
+      <c r="E53">
+        <v>-0.7633587786259542</v>
+      </c>
+      <c r="F53">
         <v>6.55</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <v>6.5</v>
       </c>
       <c r="G53">
         <v>6.55</v>
       </c>
       <c r="H53">
+        <v>6.45</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>53700</v>
+      </c>
+      <c r="L53">
+        <v>348.25</v>
+      </c>
+      <c r="M53">
+        <v>11600</v>
+      </c>
+      <c r="N53">
+        <v>6.45</v>
+      </c>
+      <c r="O53">
         <v>6.5</v>
       </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>16000</v>
-      </c>
-      <c r="L53">
-        <v>104.05</v>
-      </c>
-      <c r="M53">
-        <v>42400</v>
-      </c>
-      <c r="N53">
-        <v>6.5</v>
-      </c>
-      <c r="O53">
-        <v>6.55</v>
-      </c>
       <c r="P53">
-        <v>24400</v>
+        <v>700</v>
       </c>
     </row>
     <row r="54">
@@ -2683,38 +2683,38 @@
       <c r="B54" t="str">
         <v>-</v>
       </c>
-      <c r="C54">
-        <v>2.94</v>
-      </c>
-      <c r="D54">
-        <v>0</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54">
-        <v>2.88</v>
-      </c>
-      <c r="G54">
-        <v>2.94</v>
-      </c>
-      <c r="H54">
-        <v>2.82</v>
-      </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>2500</v>
-      </c>
-      <c r="L54">
-        <v>7.122</v>
+      <c r="C54" t="str">
+        <v>-</v>
+      </c>
+      <c r="D54" t="str">
+        <v>-</v>
+      </c>
+      <c r="E54" t="str">
+        <v>-</v>
+      </c>
+      <c r="F54" t="str">
+        <v>-</v>
+      </c>
+      <c r="G54" t="str">
+        <v>-</v>
+      </c>
+      <c r="H54" t="str">
+        <v>-</v>
+      </c>
+      <c r="I54" t="str">
+        <v>-</v>
+      </c>
+      <c r="J54" t="str">
+        <v>-</v>
+      </c>
+      <c r="K54" t="str">
+        <v>-</v>
+      </c>
+      <c r="L54" t="str">
+        <v>-</v>
       </c>
       <c r="M54">
-        <v>2000</v>
+        <v>3900</v>
       </c>
       <c r="N54">
         <v>2.82</v>
@@ -2723,7 +2723,7 @@
         <v>2.94</v>
       </c>
       <c r="P54">
-        <v>1900</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="55">
@@ -2758,13 +2758,13 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>202348</v>
+        <v>32500</v>
       </c>
       <c r="L55">
-        <v>1889.32965</v>
+        <v>303.15525</v>
       </c>
       <c r="M55">
-        <v>209100</v>
+        <v>131100</v>
       </c>
       <c r="N55">
         <v>9.3</v>
@@ -2773,7 +2773,7 @@
         <v>9.35</v>
       </c>
       <c r="P55">
-        <v>5100</v>
+        <v>180700</v>
       </c>
     </row>
     <row r="56">
@@ -2784,19 +2784,19 @@
         <v>NP</v>
       </c>
       <c r="C56">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="F56">
         <v>3.4</v>
       </c>
       <c r="G56">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="H56">
         <v>3.4</v>
@@ -2808,22 +2808,22 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>11600</v>
+        <v>80800</v>
       </c>
       <c r="L56">
-        <v>39.44</v>
+        <v>275.136</v>
       </c>
       <c r="M56">
-        <v>9000</v>
+        <v>20200</v>
       </c>
       <c r="N56">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="O56">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="P56">
-        <v>2500</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="57">
@@ -2834,13 +2834,13 @@
         <v>-</v>
       </c>
       <c r="C57">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="D57">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="E57">
-        <v>-1.8404907975460123</v>
+        <v>-1.25</v>
       </c>
       <c r="F57">
         <v>8</v>
@@ -2849,7 +2849,7 @@
         <v>8</v>
       </c>
       <c r="H57">
-        <v>8</v>
+        <v>7.65</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2858,22 +2858,22 @@
         <v>0</v>
       </c>
       <c r="K57">
+        <v>19900</v>
+      </c>
+      <c r="L57">
+        <v>152.53</v>
+      </c>
+      <c r="M57">
+        <v>200</v>
+      </c>
+      <c r="N57">
+        <v>7.7</v>
+      </c>
+      <c r="O57">
+        <v>8.05</v>
+      </c>
+      <c r="P57">
         <v>300</v>
-      </c>
-      <c r="L57">
-        <v>2.4</v>
-      </c>
-      <c r="M57">
-        <v>600</v>
-      </c>
-      <c r="N57">
-        <v>8</v>
-      </c>
-      <c r="O57">
-        <v>8.4</v>
-      </c>
-      <c r="P57">
-        <v>1300</v>
       </c>
     </row>
     <row r="58">
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="F58">
-        <v>7.3</v>
+        <v>7.35</v>
       </c>
       <c r="G58">
         <v>7.35</v>
@@ -2908,13 +2908,13 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>47215</v>
+        <v>320600</v>
       </c>
       <c r="L58">
-        <v>347.01525</v>
+        <v>2343.435</v>
       </c>
       <c r="M58">
-        <v>70800</v>
+        <v>47700</v>
       </c>
       <c r="N58">
         <v>7.3</v>
@@ -2923,7 +2923,7 @@
         <v>7.35</v>
       </c>
       <c r="P58">
-        <v>3700</v>
+        <v>106500</v>
       </c>
     </row>
     <row r="59">
@@ -2934,22 +2934,22 @@
         <v>-</v>
       </c>
       <c r="C59">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>-1.36986301369863</v>
       </c>
       <c r="F59">
         <v>7.25</v>
       </c>
       <c r="G59">
-        <v>7.35</v>
+        <v>7.25</v>
       </c>
       <c r="H59">
-        <v>7.25</v>
+        <v>7.15</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2958,22 +2958,22 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>16500</v>
+        <v>52065</v>
       </c>
       <c r="L59">
-        <v>120.405</v>
+        <v>374.61670000000004</v>
       </c>
       <c r="M59">
-        <v>5800</v>
+        <v>1500</v>
       </c>
       <c r="N59">
-        <v>7.25</v>
+        <v>7.15</v>
       </c>
       <c r="O59">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="P59">
-        <v>3400</v>
+        <v>14700</v>
       </c>
     </row>
     <row r="60">
@@ -2983,47 +2983,47 @@
       <c r="B60" t="str">
         <v>-</v>
       </c>
-      <c r="C60" t="str">
-        <v>-</v>
-      </c>
-      <c r="D60" t="str">
-        <v>-</v>
-      </c>
-      <c r="E60" t="str">
-        <v>-</v>
-      </c>
-      <c r="F60" t="str">
-        <v>-</v>
-      </c>
-      <c r="G60" t="str">
-        <v>-</v>
-      </c>
-      <c r="H60" t="str">
-        <v>-</v>
-      </c>
-      <c r="I60" t="str">
-        <v>-</v>
-      </c>
-      <c r="J60" t="str">
-        <v>-</v>
-      </c>
-      <c r="K60" t="str">
-        <v>-</v>
-      </c>
-      <c r="L60" t="str">
-        <v>-</v>
+      <c r="C60">
+        <v>7.05</v>
+      </c>
+      <c r="D60">
+        <v>-0.1</v>
+      </c>
+      <c r="E60">
+        <v>-1.3986013986013985</v>
+      </c>
+      <c r="F60">
+        <v>7.1</v>
+      </c>
+      <c r="G60">
+        <v>7.1</v>
+      </c>
+      <c r="H60">
+        <v>7.05</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>4900</v>
+      </c>
+      <c r="L60">
+        <v>34.56</v>
       </c>
       <c r="M60">
         <v>1000</v>
       </c>
       <c r="N60">
-        <v>7.05</v>
+        <v>7</v>
       </c>
       <c r="O60">
         <v>7.1</v>
       </c>
       <c r="P60">
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="61">
@@ -3033,47 +3033,47 @@
       <c r="B61" t="str">
         <v>-</v>
       </c>
-      <c r="C61" t="str">
-        <v>-</v>
-      </c>
-      <c r="D61" t="str">
-        <v>-</v>
-      </c>
-      <c r="E61" t="str">
-        <v>-</v>
-      </c>
-      <c r="F61" t="str">
-        <v>-</v>
-      </c>
-      <c r="G61" t="str">
-        <v>-</v>
-      </c>
-      <c r="H61" t="str">
-        <v>-</v>
-      </c>
-      <c r="I61" t="str">
-        <v>-</v>
-      </c>
-      <c r="J61" t="str">
-        <v>-</v>
-      </c>
-      <c r="K61" t="str">
-        <v>-</v>
-      </c>
-      <c r="L61" t="str">
-        <v>-</v>
+      <c r="C61">
+        <v>5.7</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>5.7</v>
+      </c>
+      <c r="G61">
+        <v>5.7</v>
+      </c>
+      <c r="H61">
+        <v>5.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>511</v>
+      </c>
+      <c r="L61">
+        <v>2.91325</v>
       </c>
       <c r="M61">
-        <v>10500</v>
+        <v>6200</v>
       </c>
       <c r="N61">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="O61">
         <v>5.75</v>
       </c>
       <c r="P61">
-        <v>11000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="62">
@@ -3084,22 +3084,22 @@
         <v>-</v>
       </c>
       <c r="C62">
-        <v>9.1</v>
+        <v>9.15</v>
       </c>
       <c r="D62">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E62">
-        <v>-1.0869565217391304</v>
+        <v>0.5494505494505495</v>
       </c>
       <c r="F62">
-        <v>9.1</v>
+        <v>9.15</v>
       </c>
       <c r="G62">
-        <v>9.1</v>
+        <v>9.15</v>
       </c>
       <c r="H62">
-        <v>9.1</v>
+        <v>9.15</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -3108,22 +3108,22 @@
         <v>0</v>
       </c>
       <c r="K62">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L62">
-        <v>9.1</v>
+        <v>0.915</v>
       </c>
       <c r="M62">
-        <v>800</v>
+        <v>2600</v>
       </c>
       <c r="N62">
-        <v>9.05</v>
+        <v>9</v>
       </c>
       <c r="O62">
-        <v>9.1</v>
+        <v>9.15</v>
       </c>
       <c r="P62">
-        <v>1000</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="63">
@@ -3134,46 +3134,46 @@
         <v>-</v>
       </c>
       <c r="C63">
+        <v>7.95</v>
+      </c>
+      <c r="D63">
+        <v>-0.1</v>
+      </c>
+      <c r="E63">
+        <v>-1.2422360248447204</v>
+      </c>
+      <c r="F63">
         <v>8.05</v>
-      </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-      <c r="E63">
-        <v>0</v>
-      </c>
-      <c r="F63">
-        <v>7.9</v>
       </c>
       <c r="G63">
         <v>8.05</v>
       </c>
       <c r="H63">
+        <v>7.95</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>9200</v>
+      </c>
+      <c r="L63">
+        <v>73.475</v>
+      </c>
+      <c r="M63">
+        <v>10600</v>
+      </c>
+      <c r="N63">
         <v>7.9</v>
       </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <v>10900</v>
-      </c>
-      <c r="L63">
-        <v>86.23</v>
-      </c>
-      <c r="M63">
-        <v>6400</v>
-      </c>
-      <c r="N63">
-        <v>7.95</v>
-      </c>
       <c r="O63">
-        <v>8.05</v>
+        <v>8</v>
       </c>
       <c r="P63">
-        <v>600</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="64">
@@ -3183,47 +3183,47 @@
       <c r="B64" t="str">
         <v>-</v>
       </c>
-      <c r="C64">
-        <v>1.84</v>
-      </c>
-      <c r="D64">
-        <v>0.04</v>
-      </c>
-      <c r="E64">
-        <v>2.2222222222222223</v>
-      </c>
-      <c r="F64">
-        <v>1.86</v>
-      </c>
-      <c r="G64">
-        <v>1.86</v>
-      </c>
-      <c r="H64">
-        <v>1.84</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>1300</v>
-      </c>
-      <c r="L64">
-        <v>2.394</v>
+      <c r="C64" t="str">
+        <v>-</v>
+      </c>
+      <c r="D64" t="str">
+        <v>-</v>
+      </c>
+      <c r="E64" t="str">
+        <v>-</v>
+      </c>
+      <c r="F64" t="str">
+        <v>-</v>
+      </c>
+      <c r="G64" t="str">
+        <v>-</v>
+      </c>
+      <c r="H64" t="str">
+        <v>-</v>
+      </c>
+      <c r="I64" t="str">
+        <v>-</v>
+      </c>
+      <c r="J64" t="str">
+        <v>-</v>
+      </c>
+      <c r="K64" t="str">
+        <v>-</v>
+      </c>
+      <c r="L64" t="str">
+        <v>-</v>
       </c>
       <c r="M64">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N64">
         <v>1.81</v>
       </c>
       <c r="O64">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="P64">
-        <v>4900</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65">
@@ -3234,23 +3234,23 @@
         <v>-</v>
       </c>
       <c r="C65">
-        <v>8.8</v>
+        <v>8.85</v>
       </c>
       <c r="D65">
         <v>0.05</v>
       </c>
       <c r="E65">
-        <v>0.5714285714285714</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="F65">
-        <v>8.65</v>
+        <v>8.8</v>
       </c>
       <c r="G65">
+        <v>8.9</v>
+      </c>
+      <c r="H65">
         <v>8.8</v>
       </c>
-      <c r="H65">
-        <v>8.65</v>
-      </c>
       <c r="I65">
         <v>0</v>
       </c>
@@ -3258,22 +3258,22 @@
         <v>0</v>
       </c>
       <c r="K65">
-        <v>5602</v>
+        <v>249334</v>
       </c>
       <c r="L65">
-        <v>49.03245</v>
+        <v>2202.6302</v>
       </c>
       <c r="M65">
-        <v>10600</v>
+        <v>15400</v>
       </c>
       <c r="N65">
-        <v>8.75</v>
+        <v>8.85</v>
       </c>
       <c r="O65">
-        <v>8.8</v>
+        <v>8.9</v>
       </c>
       <c r="P65">
-        <v>64600</v>
+        <v>45800</v>
       </c>
     </row>
     <row r="66">
@@ -3287,10 +3287,10 @@
         <v>22.7</v>
       </c>
       <c r="D66">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E66">
-        <v>0.4424778761061947</v>
+        <v>0</v>
       </c>
       <c r="F66">
         <v>22.7</v>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>9105</v>
+        <v>2303</v>
       </c>
       <c r="L66">
-        <v>206.6836</v>
+        <v>52.2781</v>
       </c>
       <c r="M66">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="N66">
         <v>22.6</v>
@@ -3323,7 +3323,7 @@
         <v>22.7</v>
       </c>
       <c r="P66">
-        <v>1900</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="67">
@@ -3337,16 +3337,16 @@
         <v>0.91</v>
       </c>
       <c r="D67">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E67">
-        <v>-4.2105263157894735</v>
+        <v>0</v>
       </c>
       <c r="F67">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="G67">
-        <v>0.94</v>
+        <v>0.92</v>
       </c>
       <c r="H67">
         <v>0.9</v>
@@ -3358,22 +3358,22 @@
         <v>0</v>
       </c>
       <c r="K67">
-        <v>24500</v>
+        <v>15600</v>
       </c>
       <c r="L67">
-        <v>22.336</v>
+        <v>14.291</v>
       </c>
       <c r="M67">
-        <v>400</v>
+        <v>4200</v>
       </c>
       <c r="N67">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="O67">
         <v>0.92</v>
       </c>
       <c r="P67">
-        <v>200</v>
+        <v>84400</v>
       </c>
     </row>
     <row r="68">
@@ -3384,46 +3384,46 @@
         <v>-</v>
       </c>
       <c r="C68">
+        <v>2</v>
+      </c>
+      <c r="D68">
+        <v>0.06</v>
+      </c>
+      <c r="E68">
+        <v>3.0927835051546393</v>
+      </c>
+      <c r="F68">
+        <v>2</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
+      <c r="H68">
+        <v>2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>100</v>
+      </c>
+      <c r="L68">
+        <v>0.2</v>
+      </c>
+      <c r="M68">
+        <v>500</v>
+      </c>
+      <c r="N68">
+        <v>1.92</v>
+      </c>
+      <c r="O68">
         <v>1.94</v>
       </c>
-      <c r="D68">
-        <v>-0.02</v>
-      </c>
-      <c r="E68">
-        <v>-1.0204081632653061</v>
-      </c>
-      <c r="F68">
-        <v>1.95</v>
-      </c>
-      <c r="G68">
-        <v>1.95</v>
-      </c>
-      <c r="H68">
-        <v>1.94</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <v>700</v>
-      </c>
-      <c r="L68">
-        <v>1.361</v>
-      </c>
-      <c r="M68">
-        <v>100</v>
-      </c>
-      <c r="N68">
-        <v>1.94</v>
-      </c>
-      <c r="O68">
-        <v>2</v>
-      </c>
       <c r="P68">
-        <v>300</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="69">
@@ -3434,13 +3434,13 @@
         <v>-</v>
       </c>
       <c r="C69">
-        <v>8.8</v>
+        <v>8.85</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="F69">
         <v>8.85</v>
@@ -3458,22 +3458,22 @@
         <v>0</v>
       </c>
       <c r="K69">
-        <v>26403</v>
+        <v>17100</v>
       </c>
       <c r="L69">
-        <v>233.05655</v>
+        <v>151.135</v>
       </c>
       <c r="M69">
-        <v>2300</v>
+        <v>3700</v>
       </c>
       <c r="N69">
-        <v>8.75</v>
+        <v>8.85</v>
       </c>
       <c r="O69">
-        <v>8.8</v>
+        <v>8.9</v>
       </c>
       <c r="P69">
-        <v>1800</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="70">
@@ -3493,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="F70">
-        <v>8.05</v>
+        <v>8</v>
       </c>
       <c r="G70">
         <v>8.05</v>
@@ -3508,22 +3508,22 @@
         <v>0</v>
       </c>
       <c r="K70">
-        <v>846450</v>
+        <v>164603</v>
       </c>
       <c r="L70">
-        <v>6771.9452</v>
+        <v>1316.924</v>
       </c>
       <c r="M70">
-        <v>20300</v>
+        <v>44400</v>
       </c>
       <c r="N70">
+        <v>7.95</v>
+      </c>
+      <c r="O70">
         <v>8</v>
       </c>
-      <c r="O70">
-        <v>8.05</v>
-      </c>
       <c r="P70">
-        <v>131600</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="71">
@@ -3534,13 +3534,13 @@
         <v>-</v>
       </c>
       <c r="C71">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="F71">
         <v>11.6</v>
@@ -3549,7 +3549,7 @@
         <v>11.7</v>
       </c>
       <c r="H71">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3558,22 +3558,22 @@
         <v>0</v>
       </c>
       <c r="K71">
-        <v>484312</v>
+        <v>459646</v>
       </c>
       <c r="L71">
-        <v>5621.8992</v>
+        <v>5336.021900000001</v>
       </c>
       <c r="M71">
-        <v>53200</v>
+        <v>412900</v>
       </c>
       <c r="N71">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="O71">
         <v>11.7</v>
       </c>
       <c r="P71">
-        <v>183000</v>
+        <v>596900</v>
       </c>
     </row>
   </sheetData>
